--- a/Audit Checklist in Excel/security_audit_requirements.xlsx
+++ b/Audit Checklist in Excel/security_audit_requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pp3\SECM-CAT\Audit Checklist in Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1\repositorios\SECM-CAT\Audit Checklist in Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82953D32-DB71-4E88-AC55-5869137CCE1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409489F8-C9BF-4AFE-BF00-9C289E477BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="audit" sheetId="1" r:id="rId1"/>
@@ -19,11 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">audit!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -2073,9 +2068,6 @@
     <t>The application must provide all users with the capability to manually terminate their communication session to ensure user-initiated logoff functionality.</t>
   </si>
   <si>
-    <t>Result: no for requirement SECM-CAT-IAA-114. Based on the fingerprint and the flags mapped to this requirement, the application is not compliant because at least one mapped signal contradicts the expected outcome. Contradicting signals: has_supports_manual_logout=NO (state=fail, evidence_count=0, expected=YES). This justification is derived solely from the fingerprint summaries, states, notes, and evidence counts for the mapped flags.</t>
-  </si>
-  <si>
     <t>has_supports_manual_logout</t>
   </si>
   <si>
@@ -4833,9 +4825,6 @@
     <t>Ensure the mobile health application removes all temporary files upon termination to prevent unauthorized access to sensitive data.</t>
   </si>
   <si>
-    <t>Result: yes for requirement SECM-CAT-IDS-057. Based on the fingerprint and the flags mapped to this requirement, the application is compliant because the evaluated signals support the expected secure posture and no contradicting signals were observed among the mapped flags. Key supporting signals: has_temporary_compiled_data_securely_deleted=YES (state=pass, evidence_count=14, expected=YES); has_controls_protecting_temporary_compiled_data=YES (state=pass, evidence_count=3, expected=YES). This justification is derived solely from the fingerprint summaries, states, notes, and evidence counts for the mapped flags.</t>
-  </si>
-  <si>
     <t>has_temporary_compiled_data_securely_deleted, has_controls_protecting_temporary_compiled_data</t>
   </si>
   <si>
@@ -5419,6 +5408,12 @@
   </si>
   <si>
     <t>Result: no for requirement SECM-CAT-ICR-023. Based on the fingerprint and the flags mapped to this requirement, the application is not compliant because at least one mapped signal contradicts the expected outcome. Contradicting signals: has_android_insecure_random_rng=YES (state=fail, evidence_count=18, expected=NO). This justification is derived solely from the fingerprint summaries, states, notes, and evidence counts for the mapped flags.</t>
+  </si>
+  <si>
+    <t>Result: yes for requirement SECM-CAT-IAA-114. Based on the fingerprint and the flags mapped to this requirement, the application is compliant because the evaluated signals support the expected secure posture and no contradicting signals were observed among the mapped flags. Key supporting signals: has_supports_manual_logout=YES (state=pass, evidence_count=1, expected=YES). This justification is derived solely from the fingerprint summaries, states, notes, and evidence counts for the mapped flags.</t>
+  </si>
+  <si>
+    <t>Result: no for requirement SECM-CAT-IDS-057. Based on the fingerprint and the flags mapped to this requirement, the application is not compliant because at least one mapped signal contradicts the expected outcome. Contradicting signals: has_temporary_compiled_data_securely_deleted=NO (state=fail, evidence_count=0 (Fallback verdict), expected=YES); has_controls_protecting_temporary_compiled_data=NO (state=fail, evidence_count=0 (Fallback verdict), expected=YES). This justification is derived solely from the fingerprint summaries, states, notes, and evidence counts for the mapped flags.</t>
   </si>
 </sst>
 </file>
@@ -5454,10 +5449,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5496,14 +5494,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8D0A6814-2925-4064-948E-A240D92C1506}" name="Tabla1" displayName="Tabla1" ref="A1:E470" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8D0A6814-2925-4064-948E-A240D92C1506}" name="Tabla1" displayName="Tabla1" ref="A1:E470" totalsRowShown="0" dataDxfId="5">
   <autoFilter ref="A1:E470" xr:uid="{8D0A6814-2925-4064-948E-A240D92C1506}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{0AAB7262-E5AE-4061-9AE9-658C3DDA4049}" name="id (PUID)" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{42B57F56-5325-402B-8B40-038CABE3A6B7}" name="Description (EN)" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{641E87F2-F5A0-4748-B3F7-2FBA285F1911}" name="Result" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{B3822EF4-2321-48FF-AC6F-57A9341AF735}" name="Justification (EN)" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{BCC1C6EE-1D8F-4717-959B-51EA9AC8156A}" name="Flags used" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{0AAB7262-E5AE-4061-9AE9-658C3DDA4049}" name="id (PUID)" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{42B57F56-5325-402B-8B40-038CABE3A6B7}" name="Description (EN)" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{641E87F2-F5A0-4748-B3F7-2FBA285F1911}" name="Result" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{B3822EF4-2321-48FF-AC6F-57A9341AF735}" name="Justification (EN)" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{BCC1C6EE-1D8F-4717-959B-51EA9AC8156A}" name="Flags used" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5795,16 +5793,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E470"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" customWidth="1"/>
-    <col min="4" max="4" width="57.21875" customWidth="1"/>
-    <col min="5" max="5" width="66.33203125" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="57.28515625" customWidth="1"/>
+    <col min="5" max="5" width="66.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5821,7 +5819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="360" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -5838,7 +5836,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -5855,7 +5853,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -5872,7 +5870,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -5889,7 +5887,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="225" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -5906,7 +5904,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
@@ -5923,7 +5921,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>31</v>
       </c>
@@ -5940,7 +5938,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="216" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
@@ -5957,7 +5955,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="165" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>39</v>
       </c>
@@ -5974,7 +5972,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>42</v>
       </c>
@@ -5991,7 +5989,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>46</v>
       </c>
@@ -6008,7 +6006,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>50</v>
       </c>
@@ -6025,7 +6023,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="225" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>54</v>
       </c>
@@ -6042,7 +6040,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>58</v>
       </c>
@@ -6059,7 +6057,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>62</v>
       </c>
@@ -6076,7 +6074,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>66</v>
       </c>
@@ -6093,7 +6091,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>70</v>
       </c>
@@ -6110,7 +6108,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>74</v>
       </c>
@@ -6127,7 +6125,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="360" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>79</v>
       </c>
@@ -6144,7 +6142,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>83</v>
       </c>
@@ -6161,7 +6159,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>87</v>
       </c>
@@ -6178,7 +6176,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>91</v>
       </c>
@@ -6195,7 +6193,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>95</v>
       </c>
@@ -6212,7 +6210,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>99</v>
       </c>
@@ -6227,7 +6225,7 @@
       </c>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>102</v>
       </c>
@@ -6244,7 +6242,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>106</v>
       </c>
@@ -6261,7 +6259,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>110</v>
       </c>
@@ -6278,7 +6276,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>114</v>
       </c>
@@ -6295,7 +6293,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>118</v>
       </c>
@@ -6312,7 +6310,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>122</v>
       </c>
@@ -6329,7 +6327,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>126</v>
       </c>
@@ -6346,7 +6344,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="240" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>130</v>
       </c>
@@ -6363,7 +6361,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>134</v>
       </c>
@@ -6380,7 +6378,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>138</v>
       </c>
@@ -6397,7 +6395,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="225" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>142</v>
       </c>
@@ -6414,7 +6412,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>146</v>
       </c>
@@ -6431,7 +6429,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>150</v>
       </c>
@@ -6448,7 +6446,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>154</v>
       </c>
@@ -6465,7 +6463,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="165" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>158</v>
       </c>
@@ -6482,7 +6480,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>162</v>
       </c>
@@ -6499,7 +6497,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>166</v>
       </c>
@@ -6516,7 +6514,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>170</v>
       </c>
@@ -6533,7 +6531,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>174</v>
       </c>
@@ -6550,7 +6548,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>178</v>
       </c>
@@ -6567,7 +6565,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>181</v>
       </c>
@@ -6584,7 +6582,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>185</v>
       </c>
@@ -6601,7 +6599,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>189</v>
       </c>
@@ -6618,7 +6616,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>193</v>
       </c>
@@ -6635,7 +6633,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>197</v>
       </c>
@@ -6652,7 +6650,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>201</v>
       </c>
@@ -6669,7 +6667,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>204</v>
       </c>
@@ -6686,7 +6684,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>208</v>
       </c>
@@ -6703,7 +6701,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="225" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>212</v>
       </c>
@@ -6720,7 +6718,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>216</v>
       </c>
@@ -6737,7 +6735,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="288" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>220</v>
       </c>
@@ -6754,7 +6752,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="288" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>224</v>
       </c>
@@ -6771,7 +6769,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>228</v>
       </c>
@@ -6786,7 +6784,7 @@
       </c>
       <c r="E58" s="1"/>
     </row>
-    <row r="59" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>231</v>
       </c>
@@ -6801,7 +6799,7 @@
       </c>
       <c r="E59" s="1"/>
     </row>
-    <row r="60" spans="1:5" ht="360" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>234</v>
       </c>
@@ -6818,7 +6816,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>238</v>
       </c>
@@ -6835,7 +6833,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>242</v>
       </c>
@@ -6852,7 +6850,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>246</v>
       </c>
@@ -6869,7 +6867,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="360" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>250</v>
       </c>
@@ -6884,7 +6882,7 @@
       </c>
       <c r="E64" s="1"/>
     </row>
-    <row r="65" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>253</v>
       </c>
@@ -6901,7 +6899,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>257</v>
       </c>
@@ -6916,7 +6914,7 @@
       </c>
       <c r="E66" s="1"/>
     </row>
-    <row r="67" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>260</v>
       </c>
@@ -6933,7 +6931,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>264</v>
       </c>
@@ -6950,7 +6948,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>268</v>
       </c>
@@ -6967,7 +6965,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>272</v>
       </c>
@@ -6984,7 +6982,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>275</v>
       </c>
@@ -6999,7 +6997,7 @@
       </c>
       <c r="E71" s="1"/>
     </row>
-    <row r="72" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>278</v>
       </c>
@@ -7016,7 +7014,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>282</v>
       </c>
@@ -7033,7 +7031,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>286</v>
       </c>
@@ -7050,7 +7048,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>289</v>
       </c>
@@ -7067,7 +7065,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="288" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>293</v>
       </c>
@@ -7084,7 +7082,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>297</v>
       </c>
@@ -7101,7 +7099,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="360" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>301</v>
       </c>
@@ -7118,7 +7116,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>304</v>
       </c>
@@ -7135,7 +7133,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>308</v>
       </c>
@@ -7152,7 +7150,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>312</v>
       </c>
@@ -7169,7 +7167,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" ht="165" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>316</v>
       </c>
@@ -7186,7 +7184,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" ht="165" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>320</v>
       </c>
@@ -7203,7 +7201,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="288" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>324</v>
       </c>
@@ -7220,7 +7218,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>328</v>
       </c>
@@ -7237,7 +7235,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="288" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>332</v>
       </c>
@@ -7252,7 +7250,7 @@
       </c>
       <c r="E86" s="1"/>
     </row>
-    <row r="87" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>335</v>
       </c>
@@ -7269,7 +7267,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>339</v>
       </c>
@@ -7286,7 +7284,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" ht="165" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>343</v>
       </c>
@@ -7303,7 +7301,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>347</v>
       </c>
@@ -7318,7 +7316,7 @@
       </c>
       <c r="E90" s="1"/>
     </row>
-    <row r="91" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>350</v>
       </c>
@@ -7333,7 +7331,7 @@
       </c>
       <c r="E91" s="1"/>
     </row>
-    <row r="92" spans="1:5" ht="288" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>353</v>
       </c>
@@ -7350,7 +7348,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>357</v>
       </c>
@@ -7367,7 +7365,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>361</v>
       </c>
@@ -7384,7 +7382,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="360" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>364</v>
       </c>
@@ -7401,7 +7399,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>367</v>
       </c>
@@ -7418,7 +7416,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="360" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>371</v>
       </c>
@@ -7435,7 +7433,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>375</v>
       </c>
@@ -7452,7 +7450,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>379</v>
       </c>
@@ -7469,7 +7467,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>383</v>
       </c>
@@ -7484,7 +7482,7 @@
       </c>
       <c r="E100" s="1"/>
     </row>
-    <row r="101" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" ht="240" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>386</v>
       </c>
@@ -7501,7 +7499,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>390</v>
       </c>
@@ -7518,7 +7516,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" ht="240" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>394</v>
       </c>
@@ -7535,7 +7533,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>398</v>
       </c>
@@ -7552,7 +7550,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>402</v>
       </c>
@@ -7569,7 +7567,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>405</v>
       </c>
@@ -7586,7 +7584,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>408</v>
       </c>
@@ -7603,7 +7601,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>411</v>
       </c>
@@ -7620,7 +7618,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>415</v>
       </c>
@@ -7637,7 +7635,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>419</v>
       </c>
@@ -7654,7 +7652,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>423</v>
       </c>
@@ -7671,7 +7669,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>427</v>
       </c>
@@ -7688,7 +7686,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>430</v>
       </c>
@@ -7705,7 +7703,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>434</v>
       </c>
@@ -7722,7 +7720,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>437</v>
       </c>
@@ -7739,7 +7737,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>441</v>
       </c>
@@ -7756,7 +7754,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="288" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>445</v>
       </c>
@@ -7773,7 +7771,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>449</v>
       </c>
@@ -7790,7 +7788,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>453</v>
       </c>
@@ -7807,7 +7805,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>456</v>
       </c>
@@ -7824,7 +7822,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>460</v>
       </c>
@@ -7841,7 +7839,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>464</v>
       </c>
@@ -7858,7 +7856,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>468</v>
       </c>
@@ -7875,7 +7873,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>472</v>
       </c>
@@ -7892,7 +7890,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>476</v>
       </c>
@@ -7909,7 +7907,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>480</v>
       </c>
@@ -7926,7 +7924,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>484</v>
       </c>
@@ -7943,7 +7941,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>488</v>
       </c>
@@ -7960,7 +7958,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>492</v>
       </c>
@@ -7977,7 +7975,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="360" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>496</v>
       </c>
@@ -7994,7 +7992,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="288" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>500</v>
       </c>
@@ -8011,7 +8009,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" ht="240" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>504</v>
       </c>
@@ -8028,7 +8026,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="288" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" ht="165" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>508</v>
       </c>
@@ -8045,7 +8043,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>512</v>
       </c>
@@ -8062,7 +8060,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>516</v>
       </c>
@@ -8079,7 +8077,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>520</v>
       </c>
@@ -8096,7 +8094,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>524</v>
       </c>
@@ -8113,7 +8111,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>528</v>
       </c>
@@ -8130,7 +8128,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>532</v>
       </c>
@@ -8147,7 +8145,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>536</v>
       </c>
@@ -8164,7 +8162,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>539</v>
       </c>
@@ -8181,7 +8179,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>543</v>
       </c>
@@ -8198,7 +8196,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>547</v>
       </c>
@@ -8215,7 +8213,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>551</v>
       </c>
@@ -8232,7 +8230,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>555</v>
       </c>
@@ -8249,7 +8247,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>559</v>
       </c>
@@ -8266,7 +8264,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="360" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>563</v>
       </c>
@@ -8283,7 +8281,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" ht="165" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>567</v>
       </c>
@@ -8298,7 +8296,7 @@
       </c>
       <c r="E148" s="1"/>
     </row>
-    <row r="149" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>570</v>
       </c>
@@ -8315,7 +8313,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>574</v>
       </c>
@@ -8332,7 +8330,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>578</v>
       </c>
@@ -8349,7 +8347,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>582</v>
       </c>
@@ -8366,7 +8364,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>586</v>
       </c>
@@ -8383,7 +8381,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>589</v>
       </c>
@@ -8400,7 +8398,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>592</v>
       </c>
@@ -8417,7 +8415,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>596</v>
       </c>
@@ -8434,7 +8432,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="360" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>600</v>
       </c>
@@ -8449,7 +8447,7 @@
       </c>
       <c r="E157" s="1"/>
     </row>
-    <row r="158" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>603</v>
       </c>
@@ -8464,7 +8462,7 @@
       </c>
       <c r="E158" s="1"/>
     </row>
-    <row r="159" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>606</v>
       </c>
@@ -8481,7 +8479,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>610</v>
       </c>
@@ -8496,7 +8494,7 @@
       </c>
       <c r="E160" s="1"/>
     </row>
-    <row r="161" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>613</v>
       </c>
@@ -8513,7 +8511,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>617</v>
       </c>
@@ -8530,7 +8528,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>621</v>
       </c>
@@ -8545,7 +8543,7 @@
       </c>
       <c r="E163" s="1"/>
     </row>
-    <row r="164" spans="1:5" ht="360" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>624</v>
       </c>
@@ -8562,7 +8560,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>628</v>
       </c>
@@ -8579,7 +8577,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>632</v>
       </c>
@@ -8596,7 +8594,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" ht="165" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>636</v>
       </c>
@@ -8613,7 +8611,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>640</v>
       </c>
@@ -8630,7 +8628,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>644</v>
       </c>
@@ -8647,7 +8645,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>648</v>
       </c>
@@ -8664,7 +8662,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>652</v>
       </c>
@@ -8681,7 +8679,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>656</v>
       </c>
@@ -8698,7 +8696,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>659</v>
       </c>
@@ -8715,7 +8713,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>663</v>
       </c>
@@ -8732,7 +8730,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>667</v>
       </c>
@@ -8749,7 +8747,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" ht="165" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>671</v>
       </c>
@@ -8766,7 +8764,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>675</v>
       </c>
@@ -8783,4961 +8781,4961 @@
         <v>678</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A178" s="1" t="s">
+    <row r="178" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="B178" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D178" s="1" t="s">
+      <c r="C178" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="E178" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="E178" s="1" t="s">
+    </row>
+    <row r="179" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="179" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A179" s="1" t="s">
+      <c r="B179" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D179" s="1" t="s">
+      <c r="E179" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="E179" s="1" t="s">
+    </row>
+    <row r="180" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="180" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A180" s="1" t="s">
+      <c r="B180" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="C180" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>688</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>689</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D181" s="1" t="s">
+      <c r="E181" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="E181" s="1" t="s">
+    </row>
+    <row r="182" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A182" s="1" t="s">
+      <c r="B182" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="C182" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D182" s="1" t="s">
+      <c r="E182" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="E182" s="1" t="s">
+    </row>
+    <row r="183" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="183" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A183" s="1" t="s">
+      <c r="B183" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D183" s="1" t="s">
+      <c r="E183" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="E183" s="1" t="s">
+    </row>
+    <row r="184" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A184" s="1" t="s">
+      <c r="B184" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D184" s="1" t="s">
+      <c r="E184" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="E184" s="1" t="s">
+    </row>
+    <row r="185" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="185" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A185" s="1" t="s">
+      <c r="B185" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="C185" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="C185" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D185" s="1" t="s">
+      <c r="E185" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="E185" s="1" t="s">
+    </row>
+    <row r="186" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A186" s="1" t="s">
+      <c r="B186" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="C186" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D186" s="1" t="s">
+      <c r="E186" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="E186" s="1" t="s">
+    </row>
+    <row r="187" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="187" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A187" s="1" t="s">
+      <c r="B187" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D187" s="1" t="s">
+      <c r="E187" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="E187" s="1" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A188" s="1" t="s">
+      <c r="B188" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="C188" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D188" s="1" t="s">
+      <c r="E188" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="E188" s="1" t="s">
+    </row>
+    <row r="189" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="189" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A189" s="1" t="s">
+      <c r="B189" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="C189" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="C189" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D189" s="1" t="s">
+      <c r="E189" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="E189" s="1" t="s">
+    </row>
+    <row r="190" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="190" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A190" s="1" t="s">
+      <c r="B190" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="C190" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D190" s="1" t="s">
+      <c r="E190" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="E190" s="1" t="s">
+    </row>
+    <row r="191" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="191" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A191" s="1" t="s">
+      <c r="B191" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="C191" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="C191" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D191" s="1" t="s">
+      <c r="E191" s="1" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="E191" s="1" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A192" s="1" t="s">
+      <c r="B192" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="C192" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C192" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D192" s="1" t="s">
+      <c r="E192" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="E192" s="1" t="s">
+    </row>
+    <row r="193" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="193" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A193" s="1" t="s">
+      <c r="B193" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="B193" s="1" t="s">
+      <c r="C193" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="C193" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D193" s="1" t="s">
+      <c r="E193" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="E193" s="1" t="s">
+    </row>
+    <row r="194" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="194" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A194" s="1" t="s">
+      <c r="B194" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="C194" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D194" s="1" t="s">
+      <c r="E194" s="1" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="E194" s="1" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A195" s="1" t="s">
+      <c r="B195" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D195" s="1" t="s">
+      <c r="E195" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="E195" s="1" t="s">
+    </row>
+    <row r="196" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="196" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A196" s="1" t="s">
+      <c r="B196" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="C196" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D196" s="1" t="s">
+      <c r="E196" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="E196" s="1" t="s">
+    </row>
+    <row r="197" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="197" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A197" s="1" t="s">
+      <c r="B197" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="C197" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D197" s="1" t="s">
+      <c r="E197" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="E197" s="1" t="s">
+    </row>
+    <row r="198" spans="1:5" ht="270" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="198" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A198" s="1" t="s">
+      <c r="B198" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="C198" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D198" s="1" t="s">
+      <c r="E198" s="1" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="255" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="E198" s="1" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A199" s="1" t="s">
+      <c r="B199" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="C199" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D199" s="1" t="s">
+      <c r="E199" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="E199" s="1" t="s">
+    </row>
+    <row r="200" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="200" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A200" s="1" t="s">
+      <c r="B200" s="1" t="s">
         <v>762</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>763</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>765</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>766</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D201" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="E201" s="1" t="s">
+    </row>
+    <row r="202" spans="1:5" ht="255" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
         <v>768</v>
       </c>
-    </row>
-    <row r="202" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A202" s="1" t="s">
+      <c r="B202" s="1" t="s">
         <v>769</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>770</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D202" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="E202" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="E202" s="1" t="s">
+    </row>
+    <row r="203" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="203" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A203" s="1" t="s">
+      <c r="B203" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="C203" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D203" s="1" t="s">
+      <c r="E203" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="E203" s="1" t="s">
+    </row>
+    <row r="204" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="204" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A204" s="1" t="s">
+      <c r="B204" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="B204" s="1" t="s">
+      <c r="C204" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="C204" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D204" s="1" t="s">
+      <c r="E204" s="1" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="E204" s="1" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A205" s="1" t="s">
+      <c r="B205" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="C205" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D205" s="1" t="s">
+      <c r="E205" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="E205" s="1" t="s">
+    </row>
+    <row r="206" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="206" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A206" s="1" t="s">
+      <c r="B206" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="C206" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="C206" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D206" s="1" t="s">
+      <c r="E206" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="E206" s="1" t="s">
+    </row>
+    <row r="207" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
         <v>787</v>
       </c>
-    </row>
-    <row r="207" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A207" s="1" t="s">
+      <c r="B207" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="B207" s="1" t="s">
+      <c r="C207" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="C207" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D207" s="1" t="s">
+      <c r="E207" s="1" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="E207" s="1" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A208" s="1" t="s">
+      <c r="B208" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D208" s="1" t="s">
+      <c r="E208" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="E208" s="1" t="s">
+    </row>
+    <row r="209" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="209" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A209" s="1" t="s">
+      <c r="B209" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="B209" s="1" t="s">
+      <c r="C209" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D209" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="C209" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D209" s="1" t="s">
+      <c r="E209" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="E209" s="1" t="s">
+    </row>
+    <row r="210" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="210" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A210" s="1" t="s">
+      <c r="B210" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="B210" s="1" t="s">
+      <c r="C210" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="C210" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D210" s="1" t="s">
+      <c r="E210" s="1" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="E210" s="1" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A211" s="1" t="s">
+      <c r="B211" s="1" t="s">
         <v>802</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>803</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D211" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="E211" s="1"/>
+    </row>
+    <row r="212" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="E211" s="1"/>
-    </row>
-    <row r="212" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A212" s="1" t="s">
+      <c r="B212" s="1" t="s">
         <v>805</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>806</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D212" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="E212" s="1"/>
+    </row>
+    <row r="213" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="E212" s="1"/>
-    </row>
-    <row r="213" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A213" s="1" t="s">
+      <c r="B213" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="C213" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="C213" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D213" s="1" t="s">
+      <c r="E213" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="E213" s="1" t="s">
+    </row>
+    <row r="214" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="214" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A214" s="1" t="s">
+      <c r="B214" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="B214" s="1" t="s">
+      <c r="C214" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D214" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="C214" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D214" s="1" t="s">
+      <c r="E214" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="E214" s="1" t="s">
+    </row>
+    <row r="215" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="215" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A215" s="1" t="s">
+      <c r="B215" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D215" s="1" t="s">
+      <c r="E215" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="E215" s="1" t="s">
+    </row>
+    <row r="216" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="216" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A216" s="1" t="s">
+      <c r="B216" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="B216" s="1" t="s">
+      <c r="C216" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D216" s="1" t="s">
+      <c r="E216" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="E216" s="1" t="s">
+    </row>
+    <row r="217" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="217" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A217" s="1" t="s">
+      <c r="B217" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="B217" s="1" t="s">
+      <c r="C217" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D217" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="C217" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D217" s="1" t="s">
+      <c r="E217" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="E217" s="1" t="s">
+    </row>
+    <row r="218" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="218" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A218" s="1" t="s">
+      <c r="B218" s="1" t="s">
         <v>828</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>829</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D218" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="E218" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="E218" s="1" t="s">
+    </row>
+    <row r="219" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="219" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A219" s="1" t="s">
+      <c r="B219" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="B219" s="1" t="s">
+      <c r="C219" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>833</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>834</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>835</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>836</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D220" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="E220" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="E220" s="1" t="s">
+    </row>
+    <row r="221" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
         <v>838</v>
       </c>
-    </row>
-    <row r="221" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A221" s="1" t="s">
+      <c r="B221" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="B221" s="1" t="s">
+      <c r="C221" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D221" s="1" t="s">
         <v>840</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>841</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>842</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>843</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D222" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="E222" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="E222" s="1" t="s">
+    </row>
+    <row r="223" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
         <v>845</v>
       </c>
-    </row>
-    <row r="223" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A223" s="1" t="s">
+      <c r="B223" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="B223" s="1" t="s">
+      <c r="C223" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D223" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="C223" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D223" s="1" t="s">
+      <c r="E223" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="E223" s="1" t="s">
+    </row>
+    <row r="224" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
         <v>849</v>
       </c>
-    </row>
-    <row r="224" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A224" s="1" t="s">
+      <c r="B224" s="1" t="s">
         <v>850</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>851</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D224" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="E224" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="E224" s="1" t="s">
+    </row>
+    <row r="225" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="225" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A225" s="1" t="s">
+      <c r="B225" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="B225" s="1" t="s">
+      <c r="C225" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D225" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="C225" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D225" s="1" t="s">
+      <c r="E225" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="E225" s="1" t="s">
+    </row>
+    <row r="226" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="226" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A226" s="1" t="s">
+      <c r="B226" s="1" t="s">
         <v>858</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>859</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D226" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="E226" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="E226" s="1" t="s">
+    </row>
+    <row r="227" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
         <v>861</v>
       </c>
-    </row>
-    <row r="227" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A227" s="1" t="s">
+      <c r="B227" s="1" t="s">
         <v>862</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>863</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D227" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="E227" s="1" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A228" s="1" t="s">
+      <c r="B228" s="1" t="s">
         <v>865</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>866</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D228" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="E228" s="1" t="s">
         <v>867</v>
       </c>
-      <c r="E228" s="1" t="s">
+    </row>
+    <row r="229" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="229" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A229" s="1" t="s">
+      <c r="B229" s="1" t="s">
         <v>869</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>870</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D229" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
         <v>871</v>
       </c>
-      <c r="E229" s="1" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A230" s="1" t="s">
+      <c r="B230" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="B230" s="1" t="s">
+      <c r="C230" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D230" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="C230" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D230" s="1" t="s">
+      <c r="E230" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="E230" s="1" t="s">
+    </row>
+    <row r="231" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
         <v>875</v>
       </c>
-    </row>
-    <row r="231" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A231" s="1" t="s">
+      <c r="B231" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="B231" s="1" t="s">
+      <c r="C231" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D231" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="C231" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D231" s="1" t="s">
+      <c r="E231" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="E231" s="1" t="s">
+    </row>
+    <row r="232" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
         <v>879</v>
       </c>
-    </row>
-    <row r="232" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A232" s="1" t="s">
+      <c r="B232" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B232" s="1" t="s">
+      <c r="C232" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D232" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="C232" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D232" s="1" t="s">
+      <c r="E232" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="E232" s="1" t="s">
+    </row>
+    <row r="233" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
         <v>883</v>
       </c>
-    </row>
-    <row r="233" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A233" s="1" t="s">
+      <c r="B233" s="1" t="s">
         <v>884</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>885</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D233" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="E233" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="E233" s="1" t="s">
+    </row>
+    <row r="234" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
         <v>887</v>
       </c>
-    </row>
-    <row r="234" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A234" s="1" t="s">
+      <c r="B234" s="1" t="s">
         <v>888</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>889</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D234" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="E234" s="1" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A235" s="1" t="s">
+      <c r="B235" s="1" t="s">
         <v>891</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>892</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D235" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="E235" s="1" t="s">
         <v>893</v>
       </c>
-      <c r="E235" s="1" t="s">
+    </row>
+    <row r="236" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
         <v>894</v>
       </c>
-    </row>
-    <row r="236" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A236" s="1" t="s">
+      <c r="B236" s="1" t="s">
         <v>895</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>896</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D236" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="E236" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="E236" s="1" t="s">
+    </row>
+    <row r="237" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
         <v>898</v>
       </c>
-    </row>
-    <row r="237" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A237" s="1" t="s">
+      <c r="B237" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="B237" s="1" t="s">
+      <c r="C237" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D237" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="C237" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D237" s="1" t="s">
+      <c r="E237" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="E237" s="1" t="s">
+    </row>
+    <row r="238" spans="1:5" ht="270" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
         <v>902</v>
       </c>
-    </row>
-    <row r="238" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A238" s="1" t="s">
+      <c r="B238" s="1" t="s">
         <v>903</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>904</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D238" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="E238" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="E238" s="1" t="s">
+    </row>
+    <row r="239" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
         <v>906</v>
       </c>
-    </row>
-    <row r="239" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A239" s="1" t="s">
+      <c r="B239" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="B239" s="1" t="s">
+      <c r="C239" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D239" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="C239" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D239" s="1" t="s">
+      <c r="E239" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="E239" s="1" t="s">
+    </row>
+    <row r="240" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
         <v>910</v>
       </c>
-    </row>
-    <row r="240" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A240" s="1" t="s">
+      <c r="B240" s="1" t="s">
         <v>911</v>
       </c>
-      <c r="B240" s="1" t="s">
+      <c r="C240" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D240" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="C240" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D240" s="1" t="s">
+      <c r="E240" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="E240" s="1" t="s">
+    </row>
+    <row r="241" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
         <v>914</v>
       </c>
-    </row>
-    <row r="241" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A241" s="1" t="s">
+      <c r="B241" s="1" t="s">
         <v>915</v>
       </c>
-      <c r="B241" s="1" t="s">
+      <c r="C241" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D241" s="1" t="s">
         <v>916</v>
       </c>
-      <c r="C241" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D241" s="1" t="s">
+      <c r="E241" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="E241" s="1" t="s">
+    </row>
+    <row r="242" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="242" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A242" s="1" t="s">
+      <c r="B242" s="1" t="s">
         <v>919</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>920</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D242" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="E242" s="1"/>
+    </row>
+    <row r="243" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
         <v>921</v>
       </c>
-      <c r="E242" s="1"/>
-    </row>
-    <row r="243" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A243" s="1" t="s">
+      <c r="B243" s="1" t="s">
         <v>922</v>
-      </c>
-      <c r="B243" s="1" t="s">
-        <v>923</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D243" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="E243" s="1"/>
+    </row>
+    <row r="244" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="E243" s="1"/>
-    </row>
-    <row r="244" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A244" s="1" t="s">
+      <c r="B244" s="1" t="s">
         <v>925</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>926</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D244" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="E244" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="E244" s="1" t="s">
+    </row>
+    <row r="245" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
         <v>928</v>
       </c>
-    </row>
-    <row r="245" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A245" s="1" t="s">
+      <c r="B245" s="1" t="s">
         <v>929</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>930</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D245" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="E245" s="1" t="s">
         <v>931</v>
       </c>
-      <c r="E245" s="1" t="s">
+    </row>
+    <row r="246" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="246" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A246" s="1" t="s">
+      <c r="B246" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="B246" s="1" t="s">
+      <c r="C246" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="C246" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D246" s="1" t="s">
+      <c r="E246" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="E246" s="1" t="s">
+    </row>
+    <row r="247" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
         <v>936</v>
       </c>
-    </row>
-    <row r="247" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A247" s="1" t="s">
+      <c r="B247" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="B247" s="1" t="s">
+      <c r="C247" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D247" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="C247" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D247" s="1" t="s">
+      <c r="E247" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="E247" s="1" t="s">
+    </row>
+    <row r="248" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
         <v>940</v>
       </c>
-    </row>
-    <row r="248" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A248" s="1" t="s">
+      <c r="B248" s="1" t="s">
         <v>941</v>
       </c>
-      <c r="B248" s="1" t="s">
+      <c r="C248" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="C248" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D248" s="1" t="s">
+      <c r="E248" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="E248" s="1" t="s">
+    </row>
+    <row r="249" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
         <v>944</v>
       </c>
-    </row>
-    <row r="249" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A249" s="1" t="s">
+      <c r="B249" s="1" t="s">
         <v>945</v>
-      </c>
-      <c r="B249" s="1" t="s">
-        <v>946</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D249" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="E249" s="1" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A250" s="1" t="s">
+      <c r="B250" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="B250" s="1" t="s">
+      <c r="C250" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D250" s="1" t="s">
         <v>949</v>
       </c>
-      <c r="C250" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D250" s="1" t="s">
+      <c r="E250" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="E250" s="1" t="s">
+    </row>
+    <row r="251" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
         <v>951</v>
       </c>
-    </row>
-    <row r="251" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A251" s="1" t="s">
+      <c r="B251" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="B251" s="1" t="s">
+      <c r="C251" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D251" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="C251" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D251" s="1" t="s">
+      <c r="E251" s="1" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="E251" s="1" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A252" s="1" t="s">
+      <c r="B252" s="1" t="s">
         <v>955</v>
       </c>
-      <c r="B252" s="1" t="s">
+      <c r="C252" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D252" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="C252" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D252" s="1" t="s">
+      <c r="E252" s="1" t="s">
         <v>957</v>
       </c>
-      <c r="E252" s="1" t="s">
+    </row>
+    <row r="253" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
         <v>958</v>
       </c>
-    </row>
-    <row r="253" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A253" s="1" t="s">
+      <c r="B253" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="B253" s="1" t="s">
+      <c r="C253" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D253" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="C253" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D253" s="1" t="s">
+      <c r="E253" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="E253" s="1" t="s">
+    </row>
+    <row r="254" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
         <v>962</v>
       </c>
-    </row>
-    <row r="254" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A254" s="1" t="s">
+      <c r="B254" s="1" t="s">
         <v>963</v>
       </c>
-      <c r="B254" s="1" t="s">
+      <c r="C254" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="C254" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D254" s="1" t="s">
+      <c r="E254" s="1" t="s">
         <v>965</v>
       </c>
-      <c r="E254" s="1" t="s">
+    </row>
+    <row r="255" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
         <v>966</v>
       </c>
-    </row>
-    <row r="255" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A255" s="1" t="s">
+      <c r="B255" s="1" t="s">
         <v>967</v>
       </c>
-      <c r="B255" s="1" t="s">
+      <c r="C255" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D255" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="C255" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D255" s="1" t="s">
+      <c r="E255" s="1" t="s">
         <v>969</v>
       </c>
-      <c r="E255" s="1" t="s">
+    </row>
+    <row r="256" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
         <v>970</v>
       </c>
-    </row>
-    <row r="256" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A256" s="1" t="s">
+      <c r="B256" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="B256" s="1" t="s">
+      <c r="C256" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D256" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="C256" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D256" s="1" t="s">
+      <c r="E256" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="E256" s="1" t="s">
+    </row>
+    <row r="257" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
         <v>974</v>
       </c>
-    </row>
-    <row r="257" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A257" s="1" t="s">
+      <c r="B257" s="1" t="s">
         <v>975</v>
       </c>
-      <c r="B257" s="1" t="s">
+      <c r="C257" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="C257" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D257" s="1" t="s">
+      <c r="E257" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="E257" s="1" t="s">
+    </row>
+    <row r="258" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
         <v>978</v>
       </c>
-    </row>
-    <row r="258" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A258" s="1" t="s">
+      <c r="B258" s="1" t="s">
         <v>979</v>
       </c>
-      <c r="B258" s="1" t="s">
+      <c r="C258" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D258" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="C258" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D258" s="1" t="s">
+      <c r="E258" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="E258" s="1" t="s">
+    </row>
+    <row r="259" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
         <v>982</v>
       </c>
-    </row>
-    <row r="259" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A259" s="1" t="s">
+      <c r="B259" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="B259" s="1" t="s">
+      <c r="C259" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D259" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="C259" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D259" s="1" t="s">
+      <c r="E259" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="E259" s="1" t="s">
+    </row>
+    <row r="260" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
         <v>986</v>
       </c>
-    </row>
-    <row r="260" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A260" s="1" t="s">
+      <c r="B260" s="1" t="s">
         <v>987</v>
       </c>
-      <c r="B260" s="1" t="s">
+      <c r="C260" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D260" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="C260" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D260" s="1" t="s">
+      <c r="E260" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="E260" s="1" t="s">
+    </row>
+    <row r="261" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
         <v>990</v>
       </c>
-    </row>
-    <row r="261" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A261" s="1" t="s">
+      <c r="B261" s="1" t="s">
         <v>991</v>
-      </c>
-      <c r="B261" s="1" t="s">
-        <v>992</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D261" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="E261" s="1"/>
+    </row>
+    <row r="262" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="E261" s="1"/>
-    </row>
-    <row r="262" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A262" s="1" t="s">
+      <c r="B262" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="B262" s="1" t="s">
+      <c r="C262" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D262" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="C262" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D262" s="1" t="s">
+      <c r="E262" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="E262" s="1" t="s">
+    </row>
+    <row r="263" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
         <v>997</v>
       </c>
-    </row>
-    <row r="263" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A263" s="1" t="s">
+      <c r="B263" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="B263" s="1" t="s">
+      <c r="C263" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>999</v>
       </c>
-      <c r="C263" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D263" s="1" t="s">
+      <c r="E263" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="E263" s="1" t="s">
+    </row>
+    <row r="264" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="264" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A264" s="1" t="s">
+      <c r="B264" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="B264" s="1" t="s">
+      <c r="C264" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D264" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="C264" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D264" s="1" t="s">
+      <c r="E264" s="1" t="s">
         <v>1004</v>
       </c>
-      <c r="E264" s="1" t="s">
+    </row>
+    <row r="265" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
         <v>1005</v>
       </c>
-    </row>
-    <row r="265" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A265" s="1" t="s">
+      <c r="B265" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="B265" s="1" t="s">
+      <c r="C265" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D265" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="C265" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D265" s="1" t="s">
+      <c r="E265" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="E265" s="1" t="s">
+    </row>
+    <row r="266" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
         <v>1009</v>
       </c>
-    </row>
-    <row r="266" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A266" s="1" t="s">
+      <c r="B266" s="1" t="s">
         <v>1010</v>
       </c>
-      <c r="B266" s="1" t="s">
+      <c r="C266" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D266" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="C266" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D266" s="1" t="s">
+      <c r="E266" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="E266" s="1" t="s">
+    </row>
+    <row r="267" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
         <v>1013</v>
       </c>
-    </row>
-    <row r="267" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A267" s="1" t="s">
+      <c r="B267" s="1" t="s">
         <v>1014</v>
       </c>
-      <c r="B267" s="1" t="s">
+      <c r="C267" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D267" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="C267" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D267" s="1" t="s">
+      <c r="E267" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="E267" s="1" t="s">
+    </row>
+    <row r="268" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
         <v>1017</v>
       </c>
-    </row>
-    <row r="268" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A268" s="1" t="s">
+      <c r="B268" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="B268" s="1" t="s">
+      <c r="C268" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D268" s="1" t="s">
         <v>1019</v>
       </c>
-      <c r="C268" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D268" s="1" t="s">
+      <c r="E268" s="1" t="s">
         <v>1020</v>
       </c>
-      <c r="E268" s="1" t="s">
+    </row>
+    <row r="269" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
         <v>1021</v>
       </c>
-    </row>
-    <row r="269" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A269" s="1" t="s">
+      <c r="B269" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="B269" s="1" t="s">
+      <c r="C269" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>1023</v>
       </c>
-      <c r="C269" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D269" s="1" t="s">
+      <c r="E269" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="E269" s="1" t="s">
+    </row>
+    <row r="270" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
         <v>1025</v>
       </c>
-    </row>
-    <row r="270" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A270" s="1" t="s">
+      <c r="B270" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="B270" s="1" t="s">
+      <c r="C270" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D270" s="1" t="s">
         <v>1027</v>
       </c>
-      <c r="C270" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D270" s="1" t="s">
+      <c r="E270" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="E270" s="1" t="s">
+    </row>
+    <row r="271" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
         <v>1029</v>
       </c>
-    </row>
-    <row r="271" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A271" s="1" t="s">
+      <c r="B271" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="C271" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>1031</v>
       </c>
-      <c r="C271" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D271" s="1" t="s">
+      <c r="E271" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="E271" s="1" t="s">
+    </row>
+    <row r="272" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
         <v>1033</v>
       </c>
-    </row>
-    <row r="272" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A272" s="1" t="s">
+      <c r="B272" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="B272" s="1" t="s">
+      <c r="C272" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D272" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="C272" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D272" s="1" t="s">
+      <c r="E272" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="E272" s="1" t="s">
+    </row>
+    <row r="273" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
         <v>1037</v>
       </c>
-    </row>
-    <row r="273" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A273" s="1" t="s">
+      <c r="B273" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="B273" s="1" t="s">
+      <c r="C273" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D273" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="C273" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D273" s="1" t="s">
+      <c r="E273" s="1" t="s">
         <v>1040</v>
       </c>
-      <c r="E273" s="1" t="s">
+    </row>
+    <row r="274" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
         <v>1041</v>
       </c>
-    </row>
-    <row r="274" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A274" s="1" t="s">
+      <c r="B274" s="1" t="s">
         <v>1042</v>
       </c>
-      <c r="B274" s="1" t="s">
+      <c r="C274" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D274" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="C274" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D274" s="1" t="s">
+      <c r="E274" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="E274" s="1" t="s">
+    </row>
+    <row r="275" spans="1:5" ht="315" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
         <v>1045</v>
       </c>
-    </row>
-    <row r="275" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A275" s="1" t="s">
+      <c r="B275" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="B275" s="1" t="s">
+      <c r="C275" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D275" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="C275" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D275" s="1" t="s">
+      <c r="E275" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="E275" s="1" t="s">
+    </row>
+    <row r="276" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
         <v>1049</v>
       </c>
-    </row>
-    <row r="276" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A276" s="1" t="s">
+      <c r="B276" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="B276" s="1" t="s">
+      <c r="C276" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D276" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="C276" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D276" s="1" t="s">
+      <c r="E276" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="E276" s="1" t="s">
+    </row>
+    <row r="277" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
         <v>1053</v>
       </c>
-    </row>
-    <row r="277" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A277" s="1" t="s">
+      <c r="B277" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="B277" s="1" t="s">
+      <c r="C277" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D277" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="C277" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D277" s="1" t="s">
+      <c r="E277" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="E277" s="1" t="s">
+    </row>
+    <row r="278" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
         <v>1057</v>
       </c>
-    </row>
-    <row r="278" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A278" s="1" t="s">
+      <c r="B278" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="B278" s="1" t="s">
+      <c r="C278" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D278" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="C278" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D278" s="1" t="s">
+      <c r="E278" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="E278" s="1" t="s">
+    </row>
+    <row r="279" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
         <v>1061</v>
       </c>
-    </row>
-    <row r="279" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A279" s="1" t="s">
+      <c r="B279" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="B279" s="1" t="s">
+      <c r="C279" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D279" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="C279" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D279" s="1" t="s">
+      <c r="E279" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="E279" s="1" t="s">
+    </row>
+    <row r="280" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
         <v>1065</v>
       </c>
-    </row>
-    <row r="280" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A280" s="1" t="s">
+      <c r="B280" s="1" t="s">
         <v>1066</v>
-      </c>
-      <c r="B280" s="1" t="s">
-        <v>1067</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D280" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="E280" s="1" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A281" s="1" t="s">
+      <c r="B281" s="1" t="s">
         <v>1069</v>
-      </c>
-      <c r="B281" s="1" t="s">
-        <v>1070</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D281" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E281" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="E281" s="1" t="s">
+    </row>
+    <row r="282" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
         <v>1072</v>
       </c>
-    </row>
-    <row r="282" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A282" s="1" t="s">
+      <c r="B282" s="1" t="s">
         <v>1073</v>
-      </c>
-      <c r="B282" s="1" t="s">
-        <v>1074</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D282" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E282" s="1"/>
+    </row>
+    <row r="283" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="E282" s="1"/>
-    </row>
-    <row r="283" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A283" s="1" t="s">
+      <c r="B283" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="B283" s="1" t="s">
+      <c r="C283" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D283" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="C283" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D283" s="1" t="s">
+      <c r="E283" s="1" t="s">
         <v>1078</v>
       </c>
-      <c r="E283" s="1" t="s">
+    </row>
+    <row r="284" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="284" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A284" s="1" t="s">
+      <c r="B284" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="B284" s="1" t="s">
+      <c r="C284" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D284" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="C284" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D284" s="1" t="s">
+      <c r="E284" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="E284" s="1" t="s">
+    </row>
+    <row r="285" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A285" s="1" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="285" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A285" s="1" t="s">
+      <c r="B285" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="B285" s="1" t="s">
+      <c r="C285" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D285" s="1" t="s">
         <v>1085</v>
       </c>
-      <c r="C285" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D285" s="1" t="s">
+      <c r="E285" s="1" t="s">
         <v>1086</v>
       </c>
-      <c r="E285" s="1" t="s">
+    </row>
+    <row r="286" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A286" s="1" t="s">
         <v>1087</v>
       </c>
-    </row>
-    <row r="286" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A286" s="1" t="s">
+      <c r="B286" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="B286" s="1" t="s">
+      <c r="C286" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D286" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="C286" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D286" s="1" t="s">
+      <c r="E286" s="1" t="s">
         <v>1090</v>
       </c>
-      <c r="E286" s="1" t="s">
+    </row>
+    <row r="287" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
         <v>1091</v>
       </c>
-    </row>
-    <row r="287" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A287" s="1" t="s">
+      <c r="B287" s="1" t="s">
         <v>1092</v>
       </c>
-      <c r="B287" s="1" t="s">
+      <c r="C287" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D287" s="1" t="s">
         <v>1093</v>
       </c>
-      <c r="C287" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D287" s="1" t="s">
+      <c r="E287" s="1" t="s">
         <v>1094</v>
       </c>
-      <c r="E287" s="1" t="s">
+    </row>
+    <row r="288" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A288" s="1" t="s">
         <v>1095</v>
       </c>
-    </row>
-    <row r="288" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A288" s="1" t="s">
+      <c r="B288" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="B288" s="1" t="s">
+      <c r="C288" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D288" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="C288" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D288" s="1" t="s">
+      <c r="E288" s="1" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="E288" s="1" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A289" s="1" t="s">
+      <c r="B289" s="1" t="s">
         <v>1099</v>
       </c>
-      <c r="B289" s="1" t="s">
+      <c r="C289" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D289" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="C289" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D289" s="1" t="s">
+      <c r="E289" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="E289" s="1" t="s">
+    </row>
+    <row r="290" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="290" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A290" s="1" t="s">
+      <c r="B290" s="1" t="s">
         <v>1103</v>
       </c>
-      <c r="B290" s="1" t="s">
+      <c r="C290" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D290" s="1" t="s">
         <v>1104</v>
       </c>
-      <c r="C290" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D290" s="1" t="s">
+      <c r="E290" s="1" t="s">
         <v>1105</v>
       </c>
-      <c r="E290" s="1" t="s">
+    </row>
+    <row r="291" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A291" s="1" t="s">
         <v>1106</v>
       </c>
-    </row>
-    <row r="291" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A291" s="1" t="s">
+      <c r="B291" s="1" t="s">
         <v>1107</v>
       </c>
-      <c r="B291" s="1" t="s">
+      <c r="C291" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D291" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="C291" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D291" s="1" t="s">
+      <c r="E291" s="1" t="s">
         <v>1109</v>
       </c>
-      <c r="E291" s="1" t="s">
+    </row>
+    <row r="292" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
         <v>1110</v>
       </c>
-    </row>
-    <row r="292" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A292" s="1" t="s">
+      <c r="B292" s="1" t="s">
         <v>1111</v>
       </c>
-      <c r="B292" s="1" t="s">
+      <c r="C292" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="C292" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D292" s="1" t="s">
+      <c r="E292" s="1" t="s">
         <v>1113</v>
       </c>
-      <c r="E292" s="1" t="s">
+    </row>
+    <row r="293" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A293" s="1" t="s">
         <v>1114</v>
       </c>
-    </row>
-    <row r="293" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A293" s="1" t="s">
+      <c r="B293" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="B293" s="1" t="s">
+      <c r="C293" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D293" s="1" t="s">
         <v>1116</v>
       </c>
-      <c r="C293" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D293" s="1" t="s">
+      <c r="E293" s="1" t="s">
         <v>1117</v>
       </c>
-      <c r="E293" s="1" t="s">
+    </row>
+    <row r="294" spans="1:5" ht="345" x14ac:dyDescent="0.25">
+      <c r="A294" s="1" t="s">
         <v>1118</v>
       </c>
-    </row>
-    <row r="294" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A294" s="1" t="s">
+      <c r="B294" s="1" t="s">
         <v>1119</v>
       </c>
-      <c r="B294" s="1" t="s">
+      <c r="C294" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D294" s="1" t="s">
         <v>1120</v>
       </c>
-      <c r="C294" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D294" s="1" t="s">
+      <c r="E294" s="1" t="s">
         <v>1121</v>
       </c>
-      <c r="E294" s="1" t="s">
+    </row>
+    <row r="295" spans="1:5" ht="270" x14ac:dyDescent="0.25">
+      <c r="A295" s="1" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="295" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A295" s="1" t="s">
+      <c r="B295" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="B295" s="1" t="s">
+      <c r="C295" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D295" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="C295" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D295" s="1" t="s">
+      <c r="E295" s="1" t="s">
         <v>1125</v>
       </c>
-      <c r="E295" s="1" t="s">
+    </row>
+    <row r="296" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A296" s="1" t="s">
         <v>1126</v>
       </c>
-    </row>
-    <row r="296" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A296" s="1" t="s">
+      <c r="B296" s="1" t="s">
         <v>1127</v>
       </c>
-      <c r="B296" s="1" t="s">
+      <c r="C296" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D296" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="C296" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D296" s="1" t="s">
+      <c r="E296" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="E296" s="1" t="s">
+    </row>
+    <row r="297" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A297" s="1" t="s">
         <v>1130</v>
       </c>
-    </row>
-    <row r="297" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A297" s="1" t="s">
+      <c r="B297" s="1" t="s">
         <v>1131</v>
-      </c>
-      <c r="B297" s="1" t="s">
-        <v>1132</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D297" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E297" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="E297" s="1" t="s">
+    </row>
+    <row r="298" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A298" s="1" t="s">
         <v>1134</v>
       </c>
-    </row>
-    <row r="298" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A298" s="1" t="s">
+      <c r="B298" s="1" t="s">
         <v>1135</v>
       </c>
-      <c r="B298" s="1" t="s">
+      <c r="C298" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D298" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="C298" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D298" s="1" t="s">
+      <c r="E298" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="E298" s="1" t="s">
+    </row>
+    <row r="299" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
         <v>1138</v>
       </c>
-    </row>
-    <row r="299" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A299" s="1" t="s">
+      <c r="B299" s="1" t="s">
         <v>1139</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>1140</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D299" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E299" s="1"/>
+    </row>
+    <row r="300" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
         <v>1141</v>
       </c>
-      <c r="E299" s="1"/>
-    </row>
-    <row r="300" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A300" s="1" t="s">
+      <c r="B300" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="B300" s="1" t="s">
+      <c r="C300" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D300" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="C300" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D300" s="1" t="s">
+      <c r="E300" s="1" t="s">
         <v>1144</v>
       </c>
-      <c r="E300" s="1" t="s">
+    </row>
+    <row r="301" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
         <v>1145</v>
       </c>
-    </row>
-    <row r="301" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A301" s="1" t="s">
+      <c r="B301" s="1" t="s">
         <v>1146</v>
       </c>
-      <c r="B301" s="1" t="s">
+      <c r="C301" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D301" s="1" t="s">
         <v>1147</v>
       </c>
-      <c r="C301" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D301" s="1" t="s">
+      <c r="E301" s="1" t="s">
         <v>1148</v>
       </c>
-      <c r="E301" s="1" t="s">
+    </row>
+    <row r="302" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
         <v>1149</v>
       </c>
-    </row>
-    <row r="302" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A302" s="1" t="s">
+      <c r="B302" s="1" t="s">
         <v>1150</v>
       </c>
-      <c r="B302" s="1" t="s">
+      <c r="C302" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D302" s="1" t="s">
         <v>1151</v>
       </c>
-      <c r="C302" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D302" s="1" t="s">
+      <c r="E302" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="E302" s="1" t="s">
+    </row>
+    <row r="303" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
         <v>1153</v>
       </c>
-    </row>
-    <row r="303" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A303" s="1" t="s">
+      <c r="B303" s="1" t="s">
         <v>1154</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>1155</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D303" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E303" s="1"/>
+    </row>
+    <row r="304" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="E303" s="1"/>
-    </row>
-    <row r="304" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A304" s="1" t="s">
+      <c r="B304" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="B304" s="1" t="s">
+      <c r="C304" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D304" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="C304" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D304" s="1" t="s">
+      <c r="E304" s="1" t="s">
         <v>1159</v>
       </c>
-      <c r="E304" s="1" t="s">
+    </row>
+    <row r="305" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
         <v>1160</v>
       </c>
-    </row>
-    <row r="305" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A305" s="1" t="s">
+      <c r="B305" s="1" t="s">
         <v>1161</v>
       </c>
-      <c r="B305" s="1" t="s">
+      <c r="C305" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D305" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="C305" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D305" s="1" t="s">
+      <c r="E305" s="1" t="s">
         <v>1163</v>
       </c>
-      <c r="E305" s="1" t="s">
+    </row>
+    <row r="306" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
         <v>1164</v>
       </c>
-    </row>
-    <row r="306" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A306" s="1" t="s">
+      <c r="B306" s="1" t="s">
         <v>1165</v>
       </c>
-      <c r="B306" s="1" t="s">
+      <c r="C306" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D306" s="1" t="s">
         <v>1166</v>
       </c>
-      <c r="C306" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D306" s="1" t="s">
+      <c r="E306" s="1" t="s">
         <v>1167</v>
       </c>
-      <c r="E306" s="1" t="s">
+    </row>
+    <row r="307" spans="1:5" ht="270" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
         <v>1168</v>
       </c>
-    </row>
-    <row r="307" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A307" s="1" t="s">
+      <c r="B307" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="B307" s="1" t="s">
+      <c r="C307" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D307" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="C307" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D307" s="1" t="s">
+      <c r="E307" s="1" t="s">
         <v>1171</v>
       </c>
-      <c r="E307" s="1" t="s">
+    </row>
+    <row r="308" spans="1:5" ht="255" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
         <v>1172</v>
       </c>
-    </row>
-    <row r="308" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A308" s="1" t="s">
+      <c r="B308" s="1" t="s">
         <v>1173</v>
-      </c>
-      <c r="B308" s="1" t="s">
-        <v>1174</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D308" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E308" s="1"/>
+    </row>
+    <row r="309" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
         <v>1175</v>
       </c>
-      <c r="E308" s="1"/>
-    </row>
-    <row r="309" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A309" s="1" t="s">
+      <c r="B309" s="1" t="s">
         <v>1176</v>
       </c>
-      <c r="B309" s="1" t="s">
+      <c r="C309" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D309" s="1" t="s">
         <v>1177</v>
       </c>
-      <c r="C309" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D309" s="1" t="s">
+      <c r="E309" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="E309" s="1" t="s">
+    </row>
+    <row r="310" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
         <v>1179</v>
       </c>
-    </row>
-    <row r="310" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A310" s="1" t="s">
+      <c r="B310" s="1" t="s">
         <v>1180</v>
       </c>
-      <c r="B310" s="1" t="s">
+      <c r="C310" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D310" s="1" t="s">
         <v>1181</v>
       </c>
-      <c r="C310" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D310" s="1" t="s">
+      <c r="E310" s="1" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
         <v>1182</v>
       </c>
-      <c r="E310" s="1" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A311" s="1" t="s">
+      <c r="B311" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="B311" s="1" t="s">
+      <c r="C311" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="C311" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D311" s="1" t="s">
+      <c r="E311" s="1" t="s">
         <v>1185</v>
       </c>
-      <c r="E311" s="1" t="s">
+    </row>
+    <row r="312" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
         <v>1186</v>
       </c>
-    </row>
-    <row r="312" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A312" s="1" t="s">
+      <c r="B312" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="B312" s="1" t="s">
+      <c r="C312" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D312" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="C312" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D312" s="1" t="s">
+      <c r="E312" s="1" t="s">
         <v>1189</v>
       </c>
-      <c r="E312" s="1" t="s">
+    </row>
+    <row r="313" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
         <v>1190</v>
       </c>
-    </row>
-    <row r="313" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A313" s="1" t="s">
+      <c r="B313" s="1" t="s">
         <v>1191</v>
-      </c>
-      <c r="B313" s="1" t="s">
-        <v>1192</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D313" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E313" s="1" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="E313" s="1" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A314" s="1" t="s">
+      <c r="B314" s="1" t="s">
         <v>1194</v>
       </c>
-      <c r="B314" s="1" t="s">
+      <c r="C314" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D314" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="C314" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D314" s="1" t="s">
+      <c r="E314" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="E314" s="1" t="s">
+    </row>
+    <row r="315" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="315" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A315" s="1" t="s">
+      <c r="B315" s="1" t="s">
         <v>1198</v>
-      </c>
-      <c r="B315" s="1" t="s">
-        <v>1199</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D315" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E315" s="1" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
         <v>1200</v>
       </c>
-      <c r="E315" s="1" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A316" s="1" t="s">
+      <c r="B316" s="1" t="s">
         <v>1201</v>
       </c>
-      <c r="B316" s="1" t="s">
+      <c r="C316" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D316" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="C316" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D316" s="1" t="s">
+      <c r="E316" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="E316" s="1" t="s">
+    </row>
+    <row r="317" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
         <v>1204</v>
       </c>
-    </row>
-    <row r="317" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A317" s="1" t="s">
+      <c r="B317" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="B317" s="1" t="s">
+      <c r="C317" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D317" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="C317" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D317" s="1" t="s">
+      <c r="E317" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="E317" s="1" t="s">
+    </row>
+    <row r="318" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
         <v>1208</v>
       </c>
-    </row>
-    <row r="318" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A318" s="1" t="s">
+      <c r="B318" s="1" t="s">
         <v>1209</v>
       </c>
-      <c r="B318" s="1" t="s">
+      <c r="C318" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D318" s="1" t="s">
         <v>1210</v>
       </c>
-      <c r="C318" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D318" s="1" t="s">
+      <c r="E318" s="1" t="s">
         <v>1211</v>
       </c>
-      <c r="E318" s="1" t="s">
+    </row>
+    <row r="319" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
         <v>1212</v>
       </c>
-    </row>
-    <row r="319" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A319" s="1" t="s">
+      <c r="B319" s="1" t="s">
         <v>1213</v>
       </c>
-      <c r="B319" s="1" t="s">
+      <c r="C319" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D319" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="C319" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D319" s="1" t="s">
+      <c r="E319" s="1" t="s">
         <v>1215</v>
       </c>
-      <c r="E319" s="1" t="s">
+    </row>
+    <row r="320" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
         <v>1216</v>
       </c>
-    </row>
-    <row r="320" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A320" s="1" t="s">
+      <c r="B320" s="1" t="s">
         <v>1217</v>
       </c>
-      <c r="B320" s="1" t="s">
+      <c r="C320" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D320" s="1" t="s">
         <v>1218</v>
       </c>
-      <c r="C320" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D320" s="1" t="s">
+      <c r="E320" s="1" t="s">
         <v>1219</v>
       </c>
-      <c r="E320" s="1" t="s">
+    </row>
+    <row r="321" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
         <v>1220</v>
       </c>
-    </row>
-    <row r="321" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A321" s="1" t="s">
+      <c r="B321" s="1" t="s">
         <v>1221</v>
       </c>
-      <c r="B321" s="1" t="s">
+      <c r="C321" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D321" s="1" t="s">
         <v>1222</v>
       </c>
-      <c r="C321" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D321" s="1" t="s">
+      <c r="E321" s="1" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="E321" s="1" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A322" s="1" t="s">
+      <c r="B322" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="B322" s="1" t="s">
+      <c r="C322" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>1225</v>
       </c>
-      <c r="C322" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D322" s="1" t="s">
+      <c r="E322" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="E322" s="1" t="s">
+    </row>
+    <row r="323" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
         <v>1227</v>
       </c>
-    </row>
-    <row r="323" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A323" s="1" t="s">
+      <c r="B323" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="B323" s="1" t="s">
+      <c r="C323" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D323" s="1" t="s">
         <v>1229</v>
       </c>
-      <c r="C323" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D323" s="1" t="s">
+      <c r="E323" s="1" t="s">
         <v>1230</v>
       </c>
-      <c r="E323" s="1" t="s">
+    </row>
+    <row r="324" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
         <v>1231</v>
       </c>
-    </row>
-    <row r="324" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A324" s="1" t="s">
+      <c r="B324" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="B324" s="1" t="s">
+      <c r="C324" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D324" s="1" t="s">
         <v>1233</v>
       </c>
-      <c r="C324" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D324" s="1" t="s">
+      <c r="E324" s="1" t="s">
         <v>1234</v>
       </c>
-      <c r="E324" s="1" t="s">
+    </row>
+    <row r="325" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
         <v>1235</v>
       </c>
-    </row>
-    <row r="325" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A325" s="1" t="s">
+      <c r="B325" s="1" t="s">
         <v>1236</v>
       </c>
-      <c r="B325" s="1" t="s">
+      <c r="C325" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D325" s="1" t="s">
         <v>1237</v>
       </c>
-      <c r="C325" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D325" s="1" t="s">
+      <c r="E325" s="1" t="s">
         <v>1238</v>
       </c>
-      <c r="E325" s="1" t="s">
+    </row>
+    <row r="326" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
         <v>1239</v>
       </c>
-    </row>
-    <row r="326" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A326" s="1" t="s">
+      <c r="B326" s="1" t="s">
         <v>1240</v>
       </c>
-      <c r="B326" s="1" t="s">
+      <c r="C326" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D326" s="1" t="s">
         <v>1241</v>
       </c>
-      <c r="C326" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D326" s="1" t="s">
+      <c r="E326" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="E326" s="1" t="s">
+    </row>
+    <row r="327" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
         <v>1243</v>
       </c>
-    </row>
-    <row r="327" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A327" s="1" t="s">
+      <c r="B327" s="1" t="s">
         <v>1244</v>
       </c>
-      <c r="B327" s="1" t="s">
+      <c r="C327" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D327" s="1" t="s">
         <v>1245</v>
       </c>
-      <c r="C327" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D327" s="1" t="s">
+      <c r="E327" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="E327" s="1" t="s">
+    </row>
+    <row r="328" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
         <v>1247</v>
       </c>
-    </row>
-    <row r="328" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A328" s="1" t="s">
+      <c r="B328" s="1" t="s">
         <v>1248</v>
       </c>
-      <c r="B328" s="1" t="s">
+      <c r="C328" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>1249</v>
       </c>
-      <c r="C328" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D328" s="1" t="s">
+      <c r="E328" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="E328" s="1" t="s">
+    </row>
+    <row r="329" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A329" s="1" t="s">
         <v>1251</v>
       </c>
-    </row>
-    <row r="329" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A329" s="1" t="s">
+      <c r="B329" s="1" t="s">
         <v>1252</v>
       </c>
-      <c r="B329" s="1" t="s">
+      <c r="C329" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D329" s="1" t="s">
         <v>1253</v>
       </c>
-      <c r="C329" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D329" s="1" t="s">
+      <c r="E329" s="1" t="s">
         <v>1254</v>
       </c>
-      <c r="E329" s="1" t="s">
+    </row>
+    <row r="330" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A330" s="1" t="s">
         <v>1255</v>
       </c>
-    </row>
-    <row r="330" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A330" s="1" t="s">
+      <c r="B330" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="B330" s="1" t="s">
+      <c r="C330" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D330" s="1" t="s">
         <v>1257</v>
       </c>
-      <c r="C330" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D330" s="1" t="s">
+      <c r="E330" s="1" t="s">
         <v>1258</v>
       </c>
-      <c r="E330" s="1" t="s">
+    </row>
+    <row r="331" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A331" s="1" t="s">
         <v>1259</v>
       </c>
-    </row>
-    <row r="331" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A331" s="1" t="s">
+      <c r="B331" s="1" t="s">
         <v>1260</v>
       </c>
-      <c r="B331" s="1" t="s">
+      <c r="C331" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D331" s="1" t="s">
         <v>1261</v>
       </c>
-      <c r="C331" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D331" s="1" t="s">
+      <c r="E331" s="1" t="s">
         <v>1262</v>
       </c>
-      <c r="E331" s="1" t="s">
+    </row>
+    <row r="332" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A332" s="1" t="s">
         <v>1263</v>
       </c>
-    </row>
-    <row r="332" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A332" s="1" t="s">
+      <c r="B332" s="1" t="s">
         <v>1264</v>
-      </c>
-      <c r="B332" s="1" t="s">
-        <v>1265</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D332" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E332" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="E332" s="1" t="s">
+    </row>
+    <row r="333" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A333" s="1" t="s">
         <v>1267</v>
       </c>
-    </row>
-    <row r="333" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A333" s="1" t="s">
+      <c r="B333" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="B333" s="1" t="s">
+      <c r="C333" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="C333" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D333" s="1" t="s">
+      <c r="E333" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="E333" s="1" t="s">
+    </row>
+    <row r="334" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
         <v>1271</v>
       </c>
-    </row>
-    <row r="334" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A334" s="1" t="s">
+      <c r="B334" s="1" t="s">
         <v>1272</v>
-      </c>
-      <c r="B334" s="1" t="s">
-        <v>1273</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D334" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E334" s="1" t="s">
         <v>1274</v>
       </c>
-      <c r="E334" s="1" t="s">
+    </row>
+    <row r="335" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
         <v>1275</v>
       </c>
-    </row>
-    <row r="335" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A335" s="1" t="s">
+      <c r="B335" s="1" t="s">
         <v>1276</v>
       </c>
-      <c r="B335" s="1" t="s">
+      <c r="C335" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D335" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="C335" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D335" s="1" t="s">
+      <c r="E335" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="E335" s="1" t="s">
+    </row>
+    <row r="336" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
         <v>1279</v>
       </c>
-    </row>
-    <row r="336" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A336" s="1" t="s">
+      <c r="B336" s="1" t="s">
         <v>1280</v>
       </c>
-      <c r="B336" s="1" t="s">
+      <c r="C336" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D336" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="C336" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D336" s="1" t="s">
+      <c r="E336" s="1" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
         <v>1282</v>
       </c>
-      <c r="E336" s="1" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A337" s="1" t="s">
+      <c r="B337" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="B337" s="1" t="s">
+      <c r="C337" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D337" s="1" t="s">
         <v>1284</v>
       </c>
-      <c r="C337" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D337" s="1" t="s">
+      <c r="E337" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="E337" s="1" t="s">
+    </row>
+    <row r="338" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
         <v>1286</v>
       </c>
-    </row>
-    <row r="338" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A338" s="1" t="s">
+      <c r="B338" s="1" t="s">
         <v>1287</v>
       </c>
-      <c r="B338" s="1" t="s">
+      <c r="C338" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="C338" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D338" s="1" t="s">
+      <c r="E338" s="1" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
         <v>1289</v>
       </c>
-      <c r="E338" s="1" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="339" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A339" s="1" t="s">
+      <c r="B339" s="1" t="s">
         <v>1290</v>
       </c>
-      <c r="B339" s="1" t="s">
+      <c r="C339" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D339" s="1" t="s">
         <v>1291</v>
       </c>
-      <c r="C339" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D339" s="1" t="s">
+      <c r="E339" s="1" t="s">
         <v>1292</v>
       </c>
-      <c r="E339" s="1" t="s">
+    </row>
+    <row r="340" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
         <v>1293</v>
       </c>
-    </row>
-    <row r="340" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A340" s="1" t="s">
+      <c r="B340" s="1" t="s">
         <v>1294</v>
       </c>
-      <c r="B340" s="1" t="s">
+      <c r="C340" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D340" s="1" t="s">
         <v>1295</v>
       </c>
-      <c r="C340" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D340" s="1" t="s">
+      <c r="E340" s="1" t="s">
         <v>1296</v>
       </c>
-      <c r="E340" s="1" t="s">
+    </row>
+    <row r="341" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
         <v>1297</v>
       </c>
-    </row>
-    <row r="341" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A341" s="1" t="s">
+      <c r="B341" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="B341" s="1" t="s">
+      <c r="C341" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D341" s="1" t="s">
         <v>1299</v>
       </c>
-      <c r="C341" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D341" s="1" t="s">
+      <c r="E341" s="1" t="s">
         <v>1300</v>
       </c>
-      <c r="E341" s="1" t="s">
+    </row>
+    <row r="342" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A342" s="1" t="s">
         <v>1301</v>
       </c>
-    </row>
-    <row r="342" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A342" s="1" t="s">
+      <c r="B342" s="1" t="s">
         <v>1302</v>
       </c>
-      <c r="B342" s="1" t="s">
+      <c r="C342" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D342" s="1" t="s">
         <v>1303</v>
       </c>
-      <c r="C342" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D342" s="1" t="s">
+      <c r="E342" s="1" t="s">
         <v>1304</v>
       </c>
-      <c r="E342" s="1" t="s">
+    </row>
+    <row r="343" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A343" s="1" t="s">
         <v>1305</v>
       </c>
-    </row>
-    <row r="343" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A343" s="1" t="s">
+      <c r="B343" s="1" t="s">
         <v>1306</v>
       </c>
-      <c r="B343" s="1" t="s">
+      <c r="C343" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D343" s="1" t="s">
         <v>1307</v>
       </c>
-      <c r="C343" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D343" s="1" t="s">
+      <c r="E343" s="1" t="s">
         <v>1308</v>
       </c>
-      <c r="E343" s="1" t="s">
+    </row>
+    <row r="344" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A344" s="1" t="s">
         <v>1309</v>
       </c>
-    </row>
-    <row r="344" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A344" s="1" t="s">
+      <c r="B344" s="1" t="s">
         <v>1310</v>
-      </c>
-      <c r="B344" s="1" t="s">
-        <v>1311</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D344" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E344" s="1" t="s">
         <v>1312</v>
       </c>
-      <c r="E344" s="1" t="s">
+    </row>
+    <row r="345" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A345" s="1" t="s">
         <v>1313</v>
       </c>
-    </row>
-    <row r="345" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A345" s="1" t="s">
+      <c r="B345" s="1" t="s">
         <v>1314</v>
       </c>
-      <c r="B345" s="1" t="s">
+      <c r="C345" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D345" s="1" t="s">
         <v>1315</v>
       </c>
-      <c r="C345" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D345" s="1" t="s">
+      <c r="E345" s="1" t="s">
         <v>1316</v>
       </c>
-      <c r="E345" s="1" t="s">
+    </row>
+    <row r="346" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A346" s="1" t="s">
         <v>1317</v>
       </c>
-    </row>
-    <row r="346" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A346" s="1" t="s">
+      <c r="B346" s="1" t="s">
         <v>1318</v>
       </c>
-      <c r="B346" s="1" t="s">
+      <c r="C346" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D346" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="C346" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D346" s="1" t="s">
+      <c r="E346" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="E346" s="1" t="s">
+    </row>
+    <row r="347" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A347" s="1" t="s">
         <v>1321</v>
       </c>
-    </row>
-    <row r="347" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A347" s="1" t="s">
+      <c r="B347" s="1" t="s">
         <v>1322</v>
       </c>
-      <c r="B347" s="1" t="s">
+      <c r="C347" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D347" s="1" t="s">
         <v>1323</v>
       </c>
-      <c r="C347" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D347" s="1" t="s">
+      <c r="E347" s="1" t="s">
         <v>1324</v>
       </c>
-      <c r="E347" s="1" t="s">
+    </row>
+    <row r="348" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
         <v>1325</v>
       </c>
-    </row>
-    <row r="348" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A348" s="1" t="s">
+      <c r="B348" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="B348" s="1" t="s">
+      <c r="C348" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D348" s="1" t="s">
         <v>1327</v>
       </c>
-      <c r="C348" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D348" s="1" t="s">
+      <c r="E348" s="1" t="s">
         <v>1328</v>
       </c>
-      <c r="E348" s="1" t="s">
+    </row>
+    <row r="349" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A349" s="1" t="s">
         <v>1329</v>
       </c>
-    </row>
-    <row r="349" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A349" s="1" t="s">
+      <c r="B349" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="B349" s="1" t="s">
+      <c r="C349" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D349" s="1" t="s">
         <v>1331</v>
       </c>
-      <c r="C349" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D349" s="1" t="s">
+      <c r="E349" s="1" t="s">
         <v>1332</v>
       </c>
-      <c r="E349" s="1" t="s">
+    </row>
+    <row r="350" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="350" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A350" s="1" t="s">
+      <c r="B350" s="1" t="s">
         <v>1334</v>
-      </c>
-      <c r="B350" s="1" t="s">
-        <v>1335</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D350" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E350" s="1" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A351" s="1" t="s">
         <v>1336</v>
       </c>
-      <c r="E350" s="1" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="351" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A351" s="1" t="s">
+      <c r="B351" s="1" t="s">
         <v>1337</v>
       </c>
-      <c r="B351" s="1" t="s">
+      <c r="C351" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D351" s="1" t="s">
         <v>1338</v>
       </c>
-      <c r="C351" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D351" s="1" t="s">
+      <c r="E351" s="1" t="s">
         <v>1339</v>
       </c>
-      <c r="E351" s="1" t="s">
+    </row>
+    <row r="352" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
         <v>1340</v>
       </c>
-    </row>
-    <row r="352" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A352" s="1" t="s">
+      <c r="B352" s="1" t="s">
         <v>1341</v>
       </c>
-      <c r="B352" s="1" t="s">
+      <c r="C352" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D352" s="1" t="s">
         <v>1342</v>
       </c>
-      <c r="C352" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D352" s="1" t="s">
+      <c r="E352" s="1" t="s">
         <v>1343</v>
       </c>
-      <c r="E352" s="1" t="s">
+    </row>
+    <row r="353" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A353" s="1" t="s">
         <v>1344</v>
       </c>
-    </row>
-    <row r="353" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A353" s="1" t="s">
+      <c r="B353" s="1" t="s">
         <v>1345</v>
       </c>
-      <c r="B353" s="1" t="s">
+      <c r="C353" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D353" s="1" t="s">
         <v>1346</v>
       </c>
-      <c r="C353" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D353" s="1" t="s">
+      <c r="E353" s="1" t="s">
         <v>1347</v>
       </c>
-      <c r="E353" s="1" t="s">
+    </row>
+    <row r="354" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
         <v>1348</v>
       </c>
-    </row>
-    <row r="354" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A354" s="1" t="s">
+      <c r="B354" s="1" t="s">
         <v>1349</v>
-      </c>
-      <c r="B354" s="1" t="s">
-        <v>1350</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D354" s="1" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E354" s="1"/>
+    </row>
+    <row r="355" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
         <v>1351</v>
       </c>
-      <c r="E354" s="1"/>
-    </row>
-    <row r="355" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A355" s="1" t="s">
+      <c r="B355" s="1" t="s">
         <v>1352</v>
       </c>
-      <c r="B355" s="1" t="s">
+      <c r="C355" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D355" s="1" t="s">
         <v>1353</v>
       </c>
-      <c r="C355" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D355" s="1" t="s">
+      <c r="E355" s="1" t="s">
         <v>1354</v>
       </c>
-      <c r="E355" s="1" t="s">
+    </row>
+    <row r="356" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
         <v>1355</v>
       </c>
-    </row>
-    <row r="356" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A356" s="1" t="s">
+      <c r="B356" s="1" t="s">
         <v>1356</v>
       </c>
-      <c r="B356" s="1" t="s">
+      <c r="C356" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D356" s="1" t="s">
         <v>1357</v>
       </c>
-      <c r="C356" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D356" s="1" t="s">
+      <c r="E356" s="1" t="s">
         <v>1358</v>
       </c>
-      <c r="E356" s="1" t="s">
+    </row>
+    <row r="357" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="357" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A357" s="1" t="s">
+      <c r="B357" s="1" t="s">
         <v>1360</v>
       </c>
-      <c r="B357" s="1" t="s">
+      <c r="C357" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D357" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="C357" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D357" s="1" t="s">
+      <c r="E357" s="1" t="s">
         <v>1362</v>
       </c>
-      <c r="E357" s="1" t="s">
+    </row>
+    <row r="358" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
         <v>1363</v>
       </c>
-    </row>
-    <row r="358" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A358" s="1" t="s">
+      <c r="B358" s="1" t="s">
         <v>1364</v>
       </c>
-      <c r="B358" s="1" t="s">
+      <c r="C358" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D358" s="1" t="s">
         <v>1365</v>
       </c>
-      <c r="C358" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D358" s="1" t="s">
+      <c r="E358" s="1" t="s">
         <v>1366</v>
       </c>
-      <c r="E358" s="1" t="s">
+    </row>
+    <row r="359" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A359" s="1" t="s">
         <v>1367</v>
       </c>
-    </row>
-    <row r="359" spans="1:5" ht="216" x14ac:dyDescent="0.3">
-      <c r="A359" s="1" t="s">
+      <c r="B359" s="1" t="s">
         <v>1368</v>
       </c>
-      <c r="B359" s="1" t="s">
+      <c r="C359" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D359" s="1" t="s">
         <v>1369</v>
       </c>
-      <c r="C359" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D359" s="1" t="s">
+      <c r="E359" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="E359" s="1" t="s">
+    </row>
+    <row r="360" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A360" s="1" t="s">
         <v>1371</v>
       </c>
-    </row>
-    <row r="360" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A360" s="1" t="s">
+      <c r="B360" s="1" t="s">
         <v>1372</v>
-      </c>
-      <c r="B360" s="1" t="s">
-        <v>1373</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D360" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E360" s="1" t="s">
         <v>1374</v>
       </c>
-      <c r="E360" s="1" t="s">
+    </row>
+    <row r="361" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A361" s="1" t="s">
         <v>1375</v>
       </c>
-    </row>
-    <row r="361" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A361" s="1" t="s">
+      <c r="B361" s="1" t="s">
         <v>1376</v>
       </c>
-      <c r="B361" s="1" t="s">
+      <c r="C361" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D361" s="1" t="s">
         <v>1377</v>
       </c>
-      <c r="C361" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D361" s="1" t="s">
+      <c r="E361" s="1" t="s">
         <v>1378</v>
       </c>
-      <c r="E361" s="1" t="s">
+    </row>
+    <row r="362" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A362" s="1" t="s">
         <v>1379</v>
       </c>
-    </row>
-    <row r="362" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A362" s="1" t="s">
+      <c r="B362" s="1" t="s">
         <v>1380</v>
-      </c>
-      <c r="B362" s="1" t="s">
-        <v>1381</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D362" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E362" s="1" t="s">
         <v>1382</v>
       </c>
-      <c r="E362" s="1" t="s">
+    </row>
+    <row r="363" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A363" s="1" t="s">
         <v>1383</v>
       </c>
-    </row>
-    <row r="363" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A363" s="1" t="s">
+      <c r="B363" s="1" t="s">
         <v>1384</v>
       </c>
-      <c r="B363" s="1" t="s">
+      <c r="C363" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D363" s="1" t="s">
         <v>1385</v>
       </c>
-      <c r="C363" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D363" s="1" t="s">
+      <c r="E363" s="1" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A364" s="1" t="s">
         <v>1386</v>
       </c>
-      <c r="E363" s="1" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="364" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A364" s="1" t="s">
+      <c r="B364" s="1" t="s">
         <v>1387</v>
       </c>
-      <c r="B364" s="1" t="s">
+      <c r="C364" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D364" s="1" t="s">
         <v>1388</v>
       </c>
-      <c r="C364" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D364" s="1" t="s">
+      <c r="E364" s="1" t="s">
         <v>1389</v>
       </c>
-      <c r="E364" s="1" t="s">
+    </row>
+    <row r="365" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A365" s="1" t="s">
         <v>1390</v>
       </c>
-    </row>
-    <row r="365" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A365" s="1" t="s">
+      <c r="B365" s="1" t="s">
         <v>1391</v>
       </c>
-      <c r="B365" s="1" t="s">
+      <c r="C365" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D365" s="1" t="s">
         <v>1392</v>
       </c>
-      <c r="C365" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D365" s="1" t="s">
+      <c r="E365" s="1" t="s">
         <v>1393</v>
       </c>
-      <c r="E365" s="1" t="s">
+    </row>
+    <row r="366" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A366" s="1" t="s">
         <v>1394</v>
       </c>
-    </row>
-    <row r="366" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A366" s="1" t="s">
+      <c r="B366" s="1" t="s">
         <v>1395</v>
       </c>
-      <c r="B366" s="1" t="s">
+      <c r="C366" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D366" s="1" t="s">
         <v>1396</v>
       </c>
-      <c r="C366" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D366" s="1" t="s">
+      <c r="E366" s="1" t="s">
         <v>1397</v>
       </c>
-      <c r="E366" s="1" t="s">
+    </row>
+    <row r="367" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A367" s="1" t="s">
         <v>1398</v>
       </c>
-    </row>
-    <row r="367" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A367" s="1" t="s">
+      <c r="B367" s="1" t="s">
         <v>1399</v>
       </c>
-      <c r="B367" s="1" t="s">
+      <c r="C367" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D367" s="1" t="s">
         <v>1400</v>
       </c>
-      <c r="C367" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D367" s="1" t="s">
+      <c r="E367" s="1" t="s">
         <v>1401</v>
       </c>
-      <c r="E367" s="1" t="s">
+    </row>
+    <row r="368" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A368" s="1" t="s">
         <v>1402</v>
       </c>
-    </row>
-    <row r="368" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A368" s="1" t="s">
+      <c r="B368" s="1" t="s">
         <v>1403</v>
       </c>
-      <c r="B368" s="1" t="s">
+      <c r="C368" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D368" s="1" t="s">
         <v>1404</v>
       </c>
-      <c r="C368" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D368" s="1" t="s">
+      <c r="E368" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="E368" s="1" t="s">
+    </row>
+    <row r="369" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A369" s="1" t="s">
         <v>1406</v>
       </c>
-    </row>
-    <row r="369" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A369" s="1" t="s">
+      <c r="B369" s="1" t="s">
         <v>1407</v>
       </c>
-      <c r="B369" s="1" t="s">
+      <c r="C369" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D369" s="1" t="s">
         <v>1408</v>
       </c>
-      <c r="C369" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D369" s="1" t="s">
+      <c r="E369" s="1" t="s">
         <v>1409</v>
       </c>
-      <c r="E369" s="1" t="s">
+    </row>
+    <row r="370" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A370" s="1" t="s">
         <v>1410</v>
       </c>
-    </row>
-    <row r="370" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A370" s="1" t="s">
+      <c r="B370" s="1" t="s">
         <v>1411</v>
       </c>
-      <c r="B370" s="1" t="s">
+      <c r="C370" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D370" s="1" t="s">
         <v>1412</v>
       </c>
-      <c r="C370" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D370" s="1" t="s">
+      <c r="E370" s="1" t="s">
         <v>1413</v>
       </c>
-      <c r="E370" s="1" t="s">
+    </row>
+    <row r="371" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A371" s="1" t="s">
         <v>1414</v>
       </c>
-    </row>
-    <row r="371" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A371" s="1" t="s">
+      <c r="B371" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="B371" s="1" t="s">
+      <c r="C371" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D371" s="1" t="s">
         <v>1416</v>
       </c>
-      <c r="C371" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D371" s="1" t="s">
+      <c r="E371" s="1" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A372" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="E371" s="1" t="s">
-        <v>1414</v>
-      </c>
-    </row>
-    <row r="372" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A372" s="1" t="s">
+      <c r="B372" s="1" t="s">
         <v>1418</v>
       </c>
-      <c r="B372" s="1" t="s">
+      <c r="C372" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D372" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="C372" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D372" s="1" t="s">
+      <c r="E372" s="1" t="s">
         <v>1420</v>
       </c>
-      <c r="E372" s="1" t="s">
+    </row>
+    <row r="373" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A373" s="1" t="s">
         <v>1421</v>
       </c>
-    </row>
-    <row r="373" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A373" s="1" t="s">
+      <c r="B373" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="B373" s="1" t="s">
+      <c r="C373" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D373" s="1" t="s">
         <v>1423</v>
       </c>
-      <c r="C373" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D373" s="1" t="s">
+      <c r="E373" s="1" t="s">
         <v>1424</v>
       </c>
-      <c r="E373" s="1" t="s">
+    </row>
+    <row r="374" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A374" s="1" t="s">
         <v>1425</v>
       </c>
-    </row>
-    <row r="374" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A374" s="1" t="s">
+      <c r="B374" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="B374" s="1" t="s">
+      <c r="C374" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D374" s="1" t="s">
         <v>1427</v>
-      </c>
-      <c r="C374" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D374" s="1" t="s">
-        <v>1428</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B375" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="B375" s="1" t="s">
+      <c r="C375" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D375" s="1" t="s">
         <v>1430</v>
       </c>
-      <c r="C375" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D375" s="1" t="s">
+      <c r="E375" s="1" t="s">
         <v>1431</v>
       </c>
-      <c r="E375" s="1" t="s">
+    </row>
+    <row r="376" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A376" s="1" t="s">
         <v>1432</v>
       </c>
-    </row>
-    <row r="376" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A376" s="1" t="s">
+      <c r="B376" s="1" t="s">
         <v>1433</v>
       </c>
-      <c r="B376" s="1" t="s">
+      <c r="C376" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D376" s="1" t="s">
         <v>1434</v>
       </c>
-      <c r="C376" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D376" s="1" t="s">
+      <c r="E376" s="1" t="s">
         <v>1435</v>
       </c>
-      <c r="E376" s="1" t="s">
+    </row>
+    <row r="377" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A377" s="1" t="s">
         <v>1436</v>
       </c>
-    </row>
-    <row r="377" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A377" s="1" t="s">
+      <c r="B377" s="1" t="s">
         <v>1437</v>
       </c>
-      <c r="B377" s="1" t="s">
+      <c r="C377" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D377" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="C377" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D377" s="1" t="s">
+      <c r="E377" s="1" t="s">
         <v>1439</v>
       </c>
-      <c r="E377" s="1" t="s">
+    </row>
+    <row r="378" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A378" s="1" t="s">
         <v>1440</v>
       </c>
-    </row>
-    <row r="378" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A378" s="1" t="s">
+      <c r="B378" s="1" t="s">
         <v>1441</v>
       </c>
-      <c r="B378" s="1" t="s">
+      <c r="C378" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D378" s="1" t="s">
         <v>1442</v>
       </c>
-      <c r="C378" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D378" s="1" t="s">
+      <c r="E378" s="1" t="s">
         <v>1443</v>
       </c>
-      <c r="E378" s="1" t="s">
+    </row>
+    <row r="379" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A379" s="1" t="s">
         <v>1444</v>
       </c>
-    </row>
-    <row r="379" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A379" s="1" t="s">
+      <c r="B379" s="1" t="s">
         <v>1445</v>
       </c>
-      <c r="B379" s="1" t="s">
+      <c r="C379" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D379" s="1" t="s">
         <v>1446</v>
       </c>
-      <c r="C379" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D379" s="1" t="s">
+      <c r="E379" s="1" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A380" s="1" t="s">
         <v>1447</v>
       </c>
-      <c r="E379" s="1" t="s">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="380" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A380" s="1" t="s">
+      <c r="B380" s="1" t="s">
         <v>1448</v>
       </c>
-      <c r="B380" s="1" t="s">
+      <c r="C380" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D380" s="1" t="s">
         <v>1449</v>
       </c>
-      <c r="C380" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D380" s="1" t="s">
+      <c r="E380" s="1" t="s">
         <v>1450</v>
       </c>
-      <c r="E380" s="1" t="s">
+    </row>
+    <row r="381" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A381" s="1" t="s">
         <v>1451</v>
       </c>
-    </row>
-    <row r="381" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A381" s="1" t="s">
+      <c r="B381" s="1" t="s">
         <v>1452</v>
       </c>
-      <c r="B381" s="1" t="s">
+      <c r="C381" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D381" s="1" t="s">
         <v>1453</v>
       </c>
-      <c r="C381" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D381" s="1" t="s">
+      <c r="E381" s="1" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A382" s="1" t="s">
         <v>1454</v>
       </c>
-      <c r="E381" s="1" t="s">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="382" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A382" s="1" t="s">
+      <c r="B382" s="1" t="s">
         <v>1455</v>
       </c>
-      <c r="B382" s="1" t="s">
+      <c r="C382" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D382" s="1" t="s">
         <v>1456</v>
       </c>
-      <c r="C382" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D382" s="1" t="s">
+      <c r="E382" s="1" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A383" s="1" t="s">
         <v>1457</v>
       </c>
-      <c r="E382" s="1" t="s">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="383" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A383" s="1" t="s">
+      <c r="B383" s="1" t="s">
         <v>1458</v>
       </c>
-      <c r="B383" s="1" t="s">
+      <c r="C383" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D383" s="1" t="s">
         <v>1459</v>
       </c>
-      <c r="C383" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D383" s="1" t="s">
+      <c r="E383" s="1" t="s">
         <v>1460</v>
       </c>
-      <c r="E383" s="1" t="s">
+    </row>
+    <row r="384" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A384" s="1" t="s">
         <v>1461</v>
       </c>
-    </row>
-    <row r="384" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A384" s="1" t="s">
+      <c r="B384" s="1" t="s">
         <v>1462</v>
       </c>
-      <c r="B384" s="1" t="s">
+      <c r="C384" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D384" s="1" t="s">
         <v>1463</v>
       </c>
-      <c r="C384" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D384" s="1" t="s">
+      <c r="E384" s="1" t="s">
         <v>1464</v>
       </c>
-      <c r="E384" s="1" t="s">
+    </row>
+    <row r="385" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A385" s="1" t="s">
         <v>1465</v>
       </c>
-    </row>
-    <row r="385" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A385" s="1" t="s">
+      <c r="B385" s="1" t="s">
         <v>1466</v>
       </c>
-      <c r="B385" s="1" t="s">
+      <c r="C385" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D385" s="1" t="s">
         <v>1467</v>
       </c>
-      <c r="C385" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D385" s="1" t="s">
+      <c r="E385" s="1" t="s">
         <v>1468</v>
       </c>
-      <c r="E385" s="1" t="s">
+    </row>
+    <row r="386" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A386" s="1" t="s">
         <v>1469</v>
       </c>
-    </row>
-    <row r="386" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A386" s="1" t="s">
+      <c r="B386" s="1" t="s">
         <v>1470</v>
       </c>
-      <c r="B386" s="1" t="s">
+      <c r="C386" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D386" s="1" t="s">
         <v>1471</v>
       </c>
-      <c r="C386" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D386" s="1" t="s">
+      <c r="E386" s="1" t="s">
         <v>1472</v>
       </c>
-      <c r="E386" s="1" t="s">
+    </row>
+    <row r="387" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A387" s="1" t="s">
         <v>1473</v>
       </c>
-    </row>
-    <row r="387" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A387" s="1" t="s">
+      <c r="B387" s="1" t="s">
         <v>1474</v>
       </c>
-      <c r="B387" s="1" t="s">
+      <c r="C387" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D387" s="1" t="s">
         <v>1475</v>
       </c>
-      <c r="C387" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D387" s="1" t="s">
+      <c r="E387" s="1" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A388" s="1" t="s">
         <v>1476</v>
       </c>
-      <c r="E387" s="1" t="s">
-        <v>1436</v>
-      </c>
-    </row>
-    <row r="388" spans="1:5" ht="216" x14ac:dyDescent="0.3">
-      <c r="A388" s="1" t="s">
+      <c r="B388" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="B388" s="1" t="s">
+      <c r="C388" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D388" s="1" t="s">
         <v>1478</v>
       </c>
-      <c r="C388" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D388" s="1" t="s">
+      <c r="E388" s="1" t="s">
         <v>1479</v>
       </c>
-      <c r="E388" s="1" t="s">
+    </row>
+    <row r="389" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A389" s="1" t="s">
         <v>1480</v>
       </c>
-    </row>
-    <row r="389" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A389" s="1" t="s">
+      <c r="B389" s="1" t="s">
         <v>1481</v>
       </c>
-      <c r="B389" s="1" t="s">
+      <c r="C389" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D389" s="1" t="s">
         <v>1482</v>
       </c>
-      <c r="C389" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D389" s="1" t="s">
+      <c r="E389" s="1" t="s">
         <v>1483</v>
       </c>
-      <c r="E389" s="1" t="s">
+    </row>
+    <row r="390" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A390" s="1" t="s">
         <v>1484</v>
       </c>
-    </row>
-    <row r="390" spans="1:5" ht="216" x14ac:dyDescent="0.3">
-      <c r="A390" s="1" t="s">
+      <c r="B390" s="1" t="s">
         <v>1485</v>
       </c>
-      <c r="B390" s="1" t="s">
+      <c r="C390" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D390" s="1" t="s">
         <v>1486</v>
       </c>
-      <c r="C390" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D390" s="1" t="s">
+      <c r="E390" s="1" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A391" s="1" t="s">
         <v>1487</v>
       </c>
-      <c r="E390" s="1" t="s">
-        <v>1436</v>
-      </c>
-    </row>
-    <row r="391" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A391" s="1" t="s">
+      <c r="B391" s="1" t="s">
         <v>1488</v>
       </c>
-      <c r="B391" s="1" t="s">
+      <c r="C391" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D391" s="1" t="s">
         <v>1489</v>
       </c>
-      <c r="C391" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D391" s="1" t="s">
+      <c r="E391" s="1" t="s">
         <v>1490</v>
       </c>
-      <c r="E391" s="1" t="s">
+    </row>
+    <row r="392" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A392" s="1" t="s">
         <v>1491</v>
       </c>
-    </row>
-    <row r="392" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A392" s="1" t="s">
+      <c r="B392" s="1" t="s">
         <v>1492</v>
       </c>
-      <c r="B392" s="1" t="s">
+      <c r="C392" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D392" s="1" t="s">
         <v>1493</v>
       </c>
-      <c r="C392" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D392" s="1" t="s">
+      <c r="E392" s="1" t="s">
         <v>1494</v>
       </c>
-      <c r="E392" s="1" t="s">
+    </row>
+    <row r="393" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A393" s="1" t="s">
         <v>1495</v>
       </c>
-    </row>
-    <row r="393" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A393" s="1" t="s">
+      <c r="B393" s="1" t="s">
         <v>1496</v>
       </c>
-      <c r="B393" s="1" t="s">
+      <c r="C393" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D393" s="1" t="s">
         <v>1497</v>
       </c>
-      <c r="C393" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D393" s="1" t="s">
+      <c r="E393" s="1" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A394" s="1" t="s">
         <v>1498</v>
       </c>
-      <c r="E393" s="1" t="s">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="394" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A394" s="1" t="s">
+      <c r="B394" s="1" t="s">
         <v>1499</v>
       </c>
-      <c r="B394" s="1" t="s">
+      <c r="C394" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D394" s="1" t="s">
         <v>1500</v>
       </c>
-      <c r="C394" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D394" s="1" t="s">
+      <c r="E394" s="1" t="s">
         <v>1501</v>
       </c>
-      <c r="E394" s="1" t="s">
+    </row>
+    <row r="395" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A395" s="1" t="s">
         <v>1502</v>
       </c>
-    </row>
-    <row r="395" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A395" s="1" t="s">
+      <c r="B395" s="1" t="s">
         <v>1503</v>
       </c>
-      <c r="B395" s="1" t="s">
+      <c r="C395" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D395" s="1" t="s">
         <v>1504</v>
       </c>
-      <c r="C395" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D395" s="1" t="s">
+      <c r="E395" s="1" t="s">
         <v>1505</v>
       </c>
-      <c r="E395" s="1" t="s">
+    </row>
+    <row r="396" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A396" s="1" t="s">
         <v>1506</v>
       </c>
-    </row>
-    <row r="396" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A396" s="1" t="s">
+      <c r="B396" s="1" t="s">
         <v>1507</v>
       </c>
-      <c r="B396" s="1" t="s">
+      <c r="C396" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D396" s="1" t="s">
         <v>1508</v>
       </c>
-      <c r="C396" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D396" s="1" t="s">
+      <c r="E396" s="1" t="s">
         <v>1509</v>
       </c>
-      <c r="E396" s="1" t="s">
+    </row>
+    <row r="397" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A397" s="1" t="s">
         <v>1510</v>
       </c>
-    </row>
-    <row r="397" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A397" s="1" t="s">
+      <c r="B397" s="1" t="s">
         <v>1511</v>
       </c>
-      <c r="B397" s="1" t="s">
+      <c r="C397" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D397" s="1" t="s">
         <v>1512</v>
       </c>
-      <c r="C397" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D397" s="1" t="s">
+      <c r="E397" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="E397" s="1" t="s">
+    </row>
+    <row r="398" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A398" s="1" t="s">
         <v>1514</v>
       </c>
-    </row>
-    <row r="398" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A398" s="1" t="s">
+      <c r="B398" s="1" t="s">
         <v>1515</v>
       </c>
-      <c r="B398" s="1" t="s">
+      <c r="C398" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D398" s="1" t="s">
         <v>1516</v>
-      </c>
-      <c r="C398" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D398" s="1" t="s">
-        <v>1517</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" ht="165" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B399" s="1" t="s">
         <v>1518</v>
       </c>
-      <c r="B399" s="1" t="s">
+      <c r="C399" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D399" s="1" t="s">
         <v>1519</v>
-      </c>
-      <c r="C399" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D399" s="1" t="s">
-        <v>1520</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B400" s="1" t="s">
         <v>1521</v>
       </c>
-      <c r="B400" s="1" t="s">
+      <c r="C400" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D400" s="1" t="s">
         <v>1522</v>
       </c>
-      <c r="C400" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D400" s="1" t="s">
+      <c r="E400" s="1" t="s">
         <v>1523</v>
       </c>
-      <c r="E400" s="1" t="s">
+    </row>
+    <row r="401" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A401" s="1" t="s">
         <v>1524</v>
       </c>
-    </row>
-    <row r="401" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A401" s="1" t="s">
+      <c r="B401" s="1" t="s">
         <v>1525</v>
       </c>
-      <c r="B401" s="1" t="s">
+      <c r="C401" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D401" s="1" t="s">
         <v>1526</v>
       </c>
-      <c r="C401" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D401" s="1" t="s">
+      <c r="E401" s="1" t="s">
         <v>1527</v>
       </c>
-      <c r="E401" s="1" t="s">
+    </row>
+    <row r="402" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A402" s="1" t="s">
         <v>1528</v>
       </c>
-    </row>
-    <row r="402" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A402" s="1" t="s">
+      <c r="B402" s="1" t="s">
         <v>1529</v>
       </c>
-      <c r="B402" s="1" t="s">
+      <c r="C402" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D402" s="1" t="s">
         <v>1530</v>
       </c>
-      <c r="C402" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D402" s="1" t="s">
+      <c r="E402" s="1" t="s">
         <v>1531</v>
       </c>
-      <c r="E402" s="1" t="s">
+    </row>
+    <row r="403" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A403" s="1" t="s">
         <v>1532</v>
       </c>
-    </row>
-    <row r="403" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A403" s="1" t="s">
+      <c r="B403" s="1" t="s">
         <v>1533</v>
       </c>
-      <c r="B403" s="1" t="s">
+      <c r="C403" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D403" s="1" t="s">
         <v>1534</v>
       </c>
-      <c r="C403" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D403" s="1" t="s">
+      <c r="E403" s="1" t="s">
         <v>1535</v>
       </c>
-      <c r="E403" s="1" t="s">
+    </row>
+    <row r="404" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A404" s="1" t="s">
         <v>1536</v>
       </c>
-    </row>
-    <row r="404" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A404" s="1" t="s">
+      <c r="B404" s="1" t="s">
         <v>1537</v>
       </c>
-      <c r="B404" s="1" t="s">
+      <c r="C404" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D404" s="1" t="s">
         <v>1538</v>
       </c>
-      <c r="C404" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D404" s="1" t="s">
+      <c r="E404" s="1" t="s">
         <v>1539</v>
       </c>
-      <c r="E404" s="1" t="s">
+    </row>
+    <row r="405" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A405" s="1" t="s">
         <v>1540</v>
       </c>
-    </row>
-    <row r="405" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A405" s="1" t="s">
+      <c r="B405" s="1" t="s">
         <v>1541</v>
       </c>
-      <c r="B405" s="1" t="s">
+      <c r="C405" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D405" s="1" t="s">
         <v>1542</v>
       </c>
-      <c r="C405" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D405" s="1" t="s">
+      <c r="E405" s="1" t="s">
         <v>1543</v>
       </c>
-      <c r="E405" s="1" t="s">
+    </row>
+    <row r="406" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A406" s="1" t="s">
         <v>1544</v>
       </c>
-    </row>
-    <row r="406" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A406" s="1" t="s">
+      <c r="B406" s="1" t="s">
         <v>1545</v>
       </c>
-      <c r="B406" s="1" t="s">
+      <c r="C406" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D406" s="1" t="s">
         <v>1546</v>
       </c>
-      <c r="C406" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D406" s="1" t="s">
+      <c r="E406" s="1" t="s">
         <v>1547</v>
       </c>
-      <c r="E406" s="1" t="s">
+    </row>
+    <row r="407" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A407" s="1" t="s">
         <v>1548</v>
       </c>
-    </row>
-    <row r="407" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A407" s="1" t="s">
+      <c r="B407" s="1" t="s">
         <v>1549</v>
       </c>
-      <c r="B407" s="1" t="s">
+      <c r="C407" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D407" s="1" t="s">
         <v>1550</v>
       </c>
-      <c r="C407" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D407" s="1" t="s">
+      <c r="E407" s="1" t="s">
         <v>1551</v>
       </c>
-      <c r="E407" s="1" t="s">
+    </row>
+    <row r="408" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A408" s="1" t="s">
         <v>1552</v>
       </c>
-    </row>
-    <row r="408" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A408" s="1" t="s">
+      <c r="B408" s="1" t="s">
         <v>1553</v>
       </c>
-      <c r="B408" s="1" t="s">
+      <c r="C408" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D408" s="1" t="s">
         <v>1554</v>
       </c>
-      <c r="C408" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D408" s="1" t="s">
+      <c r="E408" s="1" t="s">
         <v>1555</v>
       </c>
-      <c r="E408" s="1" t="s">
+    </row>
+    <row r="409" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A409" s="1" t="s">
         <v>1556</v>
       </c>
-    </row>
-    <row r="409" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A409" s="1" t="s">
+      <c r="B409" s="1" t="s">
         <v>1557</v>
       </c>
-      <c r="B409" s="1" t="s">
+      <c r="C409" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D409" s="1" t="s">
         <v>1558</v>
       </c>
-      <c r="C409" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D409" s="1" t="s">
+      <c r="E409" s="1" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A410" s="1" t="s">
         <v>1559</v>
       </c>
-      <c r="E409" s="1" t="s">
-        <v>1556</v>
-      </c>
-    </row>
-    <row r="410" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A410" s="1" t="s">
+      <c r="B410" s="1" t="s">
         <v>1560</v>
       </c>
-      <c r="B410" s="1" t="s">
+      <c r="C410" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D410" s="1" t="s">
         <v>1561</v>
       </c>
-      <c r="C410" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D410" s="1" t="s">
+      <c r="E410" s="1" t="s">
         <v>1562</v>
       </c>
-      <c r="E410" s="1" t="s">
+    </row>
+    <row r="411" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A411" s="1" t="s">
         <v>1563</v>
       </c>
-    </row>
-    <row r="411" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A411" s="1" t="s">
+      <c r="B411" s="1" t="s">
         <v>1564</v>
       </c>
-      <c r="B411" s="1" t="s">
+      <c r="C411" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D411" s="1" t="s">
         <v>1565</v>
       </c>
-      <c r="C411" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D411" s="1" t="s">
+      <c r="E411" s="1" t="s">
         <v>1566</v>
       </c>
-      <c r="E411" s="1" t="s">
+    </row>
+    <row r="412" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A412" s="1" t="s">
         <v>1567</v>
       </c>
-    </row>
-    <row r="412" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A412" s="1" t="s">
+      <c r="B412" s="1" t="s">
         <v>1568</v>
-      </c>
-      <c r="B412" s="1" t="s">
-        <v>1569</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D412" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E412" s="1"/>
+    </row>
+    <row r="413" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A413" s="1" t="s">
         <v>1570</v>
       </c>
-      <c r="E412" s="1"/>
-    </row>
-    <row r="413" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A413" s="1" t="s">
+      <c r="B413" s="1" t="s">
         <v>1571</v>
       </c>
-      <c r="B413" s="1" t="s">
+      <c r="C413" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D413" s="1" t="s">
         <v>1572</v>
       </c>
-      <c r="C413" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D413" s="1" t="s">
+      <c r="E413" s="1" t="s">
         <v>1573</v>
       </c>
-      <c r="E413" s="1" t="s">
+    </row>
+    <row r="414" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A414" s="1" t="s">
         <v>1574</v>
       </c>
-    </row>
-    <row r="414" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A414" s="1" t="s">
+      <c r="B414" s="1" t="s">
         <v>1575</v>
       </c>
-      <c r="B414" s="1" t="s">
+      <c r="C414" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D414" s="1" t="s">
         <v>1576</v>
       </c>
-      <c r="C414" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D414" s="1" t="s">
+      <c r="E414" s="1" t="s">
         <v>1577</v>
       </c>
-      <c r="E414" s="1" t="s">
+    </row>
+    <row r="415" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A415" s="1" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="415" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A415" s="1" t="s">
+      <c r="B415" s="1" t="s">
         <v>1579</v>
       </c>
-      <c r="B415" s="1" t="s">
+      <c r="C415" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D415" s="1" t="s">
         <v>1580</v>
       </c>
-      <c r="C415" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D415" s="1" t="s">
+      <c r="E415" s="1" t="s">
         <v>1581</v>
       </c>
-      <c r="E415" s="1" t="s">
+    </row>
+    <row r="416" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A416" s="1" t="s">
         <v>1582</v>
       </c>
-    </row>
-    <row r="416" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A416" s="1" t="s">
+      <c r="B416" s="1" t="s">
         <v>1583</v>
       </c>
-      <c r="B416" s="1" t="s">
+      <c r="C416" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D416" s="1" t="s">
         <v>1584</v>
       </c>
-      <c r="C416" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D416" s="1" t="s">
+      <c r="E416" s="1" t="s">
         <v>1585</v>
       </c>
-      <c r="E416" s="1" t="s">
+    </row>
+    <row r="417" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A417" s="1" t="s">
         <v>1586</v>
       </c>
-    </row>
-    <row r="417" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A417" s="1" t="s">
+      <c r="B417" s="1" t="s">
         <v>1587</v>
       </c>
-      <c r="B417" s="1" t="s">
+      <c r="C417" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D417" s="1" t="s">
         <v>1588</v>
       </c>
-      <c r="C417" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D417" s="1" t="s">
+      <c r="E417" s="1" t="s">
         <v>1589</v>
       </c>
-      <c r="E417" s="1" t="s">
+    </row>
+    <row r="418" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A418" s="1" t="s">
         <v>1590</v>
       </c>
-    </row>
-    <row r="418" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A418" s="1" t="s">
+      <c r="B418" s="1" t="s">
         <v>1591</v>
       </c>
-      <c r="B418" s="1" t="s">
+      <c r="C418" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D418" s="1" t="s">
         <v>1592</v>
       </c>
-      <c r="C418" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D418" s="1" t="s">
+      <c r="E418" s="1" t="s">
         <v>1593</v>
       </c>
-      <c r="E418" s="1" t="s">
+    </row>
+    <row r="419" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A419" s="1" t="s">
         <v>1594</v>
       </c>
-    </row>
-    <row r="419" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A419" s="1" t="s">
+      <c r="B419" s="1" t="s">
         <v>1595</v>
       </c>
-      <c r="B419" s="1" t="s">
+      <c r="C419" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D419" s="1" t="s">
         <v>1596</v>
       </c>
-      <c r="C419" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D419" s="1" t="s">
+      <c r="E419" s="1" t="s">
         <v>1597</v>
       </c>
-      <c r="E419" s="1" t="s">
+    </row>
+    <row r="420" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A420" s="2" t="s">
         <v>1598</v>
       </c>
-    </row>
-    <row r="420" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A420" s="1" t="s">
+      <c r="B420" s="2" t="s">
         <v>1599</v>
       </c>
-      <c r="B420" s="1" t="s">
+      <c r="C420" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D420" s="2" t="s">
+        <v>1796</v>
+      </c>
+      <c r="E420" s="2" t="s">
         <v>1600</v>
       </c>
-      <c r="C420" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D420" s="1" t="s">
+    </row>
+    <row r="421" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A421" s="1" t="s">
         <v>1601</v>
       </c>
-      <c r="E420" s="1" t="s">
+      <c r="B421" s="1" t="s">
         <v>1602</v>
       </c>
-    </row>
-    <row r="421" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A421" s="1" t="s">
+      <c r="C421" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D421" s="1" t="s">
         <v>1603</v>
       </c>
-      <c r="B421" s="1" t="s">
+      <c r="E421" s="1" t="s">
         <v>1604</v>
       </c>
-      <c r="C421" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D421" s="1" t="s">
+    </row>
+    <row r="422" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A422" s="1" t="s">
         <v>1605</v>
       </c>
-      <c r="E421" s="1" t="s">
+      <c r="B422" s="1" t="s">
         <v>1606</v>
       </c>
-    </row>
-    <row r="422" spans="1:5" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A422" s="1" t="s">
+      <c r="C422" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D422" s="1" t="s">
         <v>1607</v>
       </c>
-      <c r="B422" s="1" t="s">
+      <c r="E422" s="1" t="s">
         <v>1608</v>
       </c>
-      <c r="C422" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D422" s="1" t="s">
+    </row>
+    <row r="423" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A423" s="1" t="s">
         <v>1609</v>
       </c>
-      <c r="E422" s="1" t="s">
+      <c r="B423" s="1" t="s">
         <v>1610</v>
       </c>
-    </row>
-    <row r="423" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A423" s="1" t="s">
+      <c r="C423" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D423" s="1" t="s">
         <v>1611</v>
       </c>
-      <c r="B423" s="1" t="s">
+      <c r="E423" s="1" t="s">
         <v>1612</v>
       </c>
-      <c r="C423" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D423" s="1" t="s">
+    </row>
+    <row r="424" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A424" s="1" t="s">
         <v>1613</v>
       </c>
-      <c r="E423" s="1" t="s">
+      <c r="B424" s="1" t="s">
         <v>1614</v>
       </c>
-    </row>
-    <row r="424" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A424" s="1" t="s">
+      <c r="C424" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D424" s="1" t="s">
         <v>1615</v>
       </c>
-      <c r="B424" s="1" t="s">
+      <c r="E424" s="1" t="s">
         <v>1616</v>
       </c>
-      <c r="C424" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D424" s="1" t="s">
+    </row>
+    <row r="425" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A425" s="1" t="s">
         <v>1617</v>
       </c>
-      <c r="E424" s="1" t="s">
+      <c r="B425" s="1" t="s">
         <v>1618</v>
       </c>
-    </row>
-    <row r="425" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A425" s="1" t="s">
+      <c r="C425" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D425" s="1" t="s">
         <v>1619</v>
       </c>
-      <c r="B425" s="1" t="s">
+      <c r="E425" s="1" t="s">
         <v>1620</v>
       </c>
-      <c r="C425" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D425" s="1" t="s">
+    </row>
+    <row r="426" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A426" s="1" t="s">
         <v>1621</v>
       </c>
-      <c r="E425" s="1" t="s">
+      <c r="B426" s="1" t="s">
         <v>1622</v>
       </c>
-    </row>
-    <row r="426" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A426" s="1" t="s">
+      <c r="C426" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D426" s="1" t="s">
         <v>1623</v>
       </c>
-      <c r="B426" s="1" t="s">
+      <c r="E426" s="1" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A427" s="1" t="s">
         <v>1624</v>
       </c>
-      <c r="C426" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D426" s="1" t="s">
+      <c r="B427" s="1" t="s">
         <v>1625</v>
       </c>
-      <c r="E426" s="1" t="s">
-        <v>1614</v>
-      </c>
-    </row>
-    <row r="427" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A427" s="1" t="s">
+      <c r="C427" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D427" s="1" t="s">
         <v>1626</v>
       </c>
-      <c r="B427" s="1" t="s">
+      <c r="E427" s="1" t="s">
         <v>1627</v>
       </c>
-      <c r="C427" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D427" s="1" t="s">
+    </row>
+    <row r="428" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A428" s="1" t="s">
         <v>1628</v>
       </c>
-      <c r="E427" s="1" t="s">
+      <c r="B428" s="1" t="s">
         <v>1629</v>
       </c>
-    </row>
-    <row r="428" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A428" s="1" t="s">
+      <c r="C428" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D428" s="1" t="s">
         <v>1630</v>
       </c>
-      <c r="B428" s="1" t="s">
+      <c r="E428" s="1" t="s">
         <v>1631</v>
       </c>
-      <c r="C428" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D428" s="1" t="s">
+    </row>
+    <row r="429" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A429" s="1" t="s">
         <v>1632</v>
       </c>
-      <c r="E428" s="1" t="s">
+      <c r="B429" s="1" t="s">
         <v>1633</v>
       </c>
-    </row>
-    <row r="429" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A429" s="1" t="s">
+      <c r="C429" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D429" s="1" t="s">
         <v>1634</v>
       </c>
-      <c r="B429" s="1" t="s">
+      <c r="E429" s="1" t="s">
         <v>1635</v>
       </c>
-      <c r="C429" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D429" s="1" t="s">
+    </row>
+    <row r="430" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A430" s="1" t="s">
         <v>1636</v>
       </c>
-      <c r="E429" s="1" t="s">
+      <c r="B430" s="1" t="s">
         <v>1637</v>
       </c>
-    </row>
-    <row r="430" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A430" s="1" t="s">
+      <c r="C430" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D430" s="1" t="s">
         <v>1638</v>
       </c>
-      <c r="B430" s="1" t="s">
+      <c r="E430" s="1" t="s">
         <v>1639</v>
       </c>
-      <c r="C430" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D430" s="1" t="s">
+    </row>
+    <row r="431" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A431" s="1" t="s">
         <v>1640</v>
       </c>
-      <c r="E430" s="1" t="s">
+      <c r="B431" s="1" t="s">
         <v>1641</v>
-      </c>
-    </row>
-    <row r="431" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A431" s="1" t="s">
-        <v>1642</v>
-      </c>
-      <c r="B431" s="1" t="s">
-        <v>1643</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D431" s="1" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E431" s="1" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" ht="270" x14ac:dyDescent="0.25">
+      <c r="A432" s="1" t="s">
         <v>1644</v>
       </c>
-      <c r="E431" s="1" t="s">
+      <c r="B432" s="1" t="s">
         <v>1645</v>
       </c>
-    </row>
-    <row r="432" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A432" s="1" t="s">
+      <c r="C432" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D432" s="1" t="s">
         <v>1646</v>
       </c>
-      <c r="B432" s="1" t="s">
+      <c r="E432" s="1" t="s">
         <v>1647</v>
       </c>
-      <c r="C432" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D432" s="1" t="s">
+    </row>
+    <row r="433" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A433" s="1" t="s">
         <v>1648</v>
       </c>
-      <c r="E432" s="1" t="s">
+      <c r="B433" s="1" t="s">
         <v>1649</v>
       </c>
-    </row>
-    <row r="433" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A433" s="1" t="s">
+      <c r="C433" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D433" s="1" t="s">
         <v>1650</v>
       </c>
-      <c r="B433" s="1" t="s">
+      <c r="E433" s="1" t="s">
         <v>1651</v>
       </c>
-      <c r="C433" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D433" s="1" t="s">
+    </row>
+    <row r="434" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A434" s="1" t="s">
         <v>1652</v>
       </c>
-      <c r="E433" s="1" t="s">
+      <c r="B434" s="1" t="s">
         <v>1653</v>
       </c>
-    </row>
-    <row r="434" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A434" s="1" t="s">
+      <c r="C434" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D434" s="1" t="s">
         <v>1654</v>
       </c>
-      <c r="B434" s="1" t="s">
+      <c r="E434" s="1" t="s">
         <v>1655</v>
       </c>
-      <c r="C434" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D434" s="1" t="s">
+    </row>
+    <row r="435" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A435" s="1" t="s">
         <v>1656</v>
       </c>
-      <c r="E434" s="1" t="s">
+      <c r="B435" s="1" t="s">
         <v>1657</v>
       </c>
-    </row>
-    <row r="435" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A435" s="1" t="s">
+      <c r="C435" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D435" s="1" t="s">
         <v>1658</v>
       </c>
-      <c r="B435" s="1" t="s">
+      <c r="E435" s="1" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" ht="255" x14ac:dyDescent="0.25">
+      <c r="A436" s="1" t="s">
         <v>1659</v>
       </c>
-      <c r="C435" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D435" s="1" t="s">
+      <c r="B436" s="1" t="s">
         <v>1660</v>
       </c>
-      <c r="E435" s="1" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="436" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A436" s="1" t="s">
+      <c r="C436" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D436" s="1" t="s">
         <v>1661</v>
       </c>
-      <c r="B436" s="1" t="s">
+      <c r="E436" s="1" t="s">
         <v>1662</v>
       </c>
-      <c r="C436" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D436" s="1" t="s">
+    </row>
+    <row r="437" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A437" s="1" t="s">
         <v>1663</v>
       </c>
-      <c r="E436" s="1" t="s">
+      <c r="B437" s="1" t="s">
         <v>1664</v>
       </c>
-    </row>
-    <row r="437" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A437" s="1" t="s">
+      <c r="C437" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D437" s="1" t="s">
         <v>1665</v>
       </c>
-      <c r="B437" s="1" t="s">
+      <c r="E437" s="1" t="s">
         <v>1666</v>
       </c>
-      <c r="C437" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D437" s="1" t="s">
+    </row>
+    <row r="438" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A438" s="1" t="s">
         <v>1667</v>
       </c>
-      <c r="E437" s="1" t="s">
+      <c r="B438" s="1" t="s">
         <v>1668</v>
       </c>
-    </row>
-    <row r="438" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A438" s="1" t="s">
+      <c r="C438" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D438" s="1" t="s">
         <v>1669</v>
       </c>
-      <c r="B438" s="1" t="s">
+      <c r="E438" s="1" t="s">
         <v>1670</v>
       </c>
-      <c r="C438" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D438" s="1" t="s">
+    </row>
+    <row r="439" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A439" s="1" t="s">
         <v>1671</v>
       </c>
-      <c r="E438" s="1" t="s">
+      <c r="B439" s="1" t="s">
         <v>1672</v>
       </c>
-    </row>
-    <row r="439" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A439" s="1" t="s">
+      <c r="C439" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D439" s="1" t="s">
         <v>1673</v>
       </c>
-      <c r="B439" s="1" t="s">
+      <c r="E439" s="1" t="s">
         <v>1674</v>
       </c>
-      <c r="C439" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D439" s="1" t="s">
+    </row>
+    <row r="440" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A440" s="1" t="s">
         <v>1675</v>
       </c>
-      <c r="E439" s="1" t="s">
+      <c r="B440" s="1" t="s">
         <v>1676</v>
       </c>
-    </row>
-    <row r="440" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A440" s="1" t="s">
+      <c r="C440" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D440" s="1" t="s">
         <v>1677</v>
       </c>
-      <c r="B440" s="1" t="s">
+      <c r="E440" s="1" t="s">
         <v>1678</v>
       </c>
-      <c r="C440" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D440" s="1" t="s">
+    </row>
+    <row r="441" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A441" s="1" t="s">
         <v>1679</v>
       </c>
-      <c r="E440" s="1" t="s">
+      <c r="B441" s="1" t="s">
         <v>1680</v>
       </c>
-    </row>
-    <row r="441" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A441" s="1" t="s">
+      <c r="C441" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D441" s="1" t="s">
         <v>1681</v>
       </c>
-      <c r="B441" s="1" t="s">
+      <c r="E441" s="1" t="s">
         <v>1682</v>
       </c>
-      <c r="C441" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D441" s="1" t="s">
+    </row>
+    <row r="442" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A442" s="1" t="s">
         <v>1683</v>
       </c>
-      <c r="E441" s="1" t="s">
+      <c r="B442" s="1" t="s">
         <v>1684</v>
       </c>
-    </row>
-    <row r="442" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A442" s="1" t="s">
+      <c r="C442" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D442" s="1" t="s">
         <v>1685</v>
       </c>
-      <c r="B442" s="1" t="s">
+      <c r="E442" s="1" t="s">
         <v>1686</v>
       </c>
-      <c r="C442" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D442" s="1" t="s">
+    </row>
+    <row r="443" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A443" s="1" t="s">
         <v>1687</v>
       </c>
-      <c r="E442" s="1" t="s">
+      <c r="B443" s="1" t="s">
         <v>1688</v>
       </c>
-    </row>
-    <row r="443" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A443" s="1" t="s">
+      <c r="C443" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D443" s="1" t="s">
         <v>1689</v>
       </c>
-      <c r="B443" s="1" t="s">
+      <c r="E443" s="1" t="s">
         <v>1690</v>
       </c>
-      <c r="C443" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D443" s="1" t="s">
+    </row>
+    <row r="444" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A444" s="1" t="s">
         <v>1691</v>
       </c>
-      <c r="E443" s="1" t="s">
+      <c r="B444" s="1" t="s">
         <v>1692</v>
       </c>
-    </row>
-    <row r="444" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A444" s="1" t="s">
+      <c r="C444" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D444" s="1" t="s">
         <v>1693</v>
       </c>
-      <c r="B444" s="1" t="s">
+      <c r="E444" s="1" t="s">
         <v>1694</v>
       </c>
-      <c r="C444" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D444" s="1" t="s">
+    </row>
+    <row r="445" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A445" s="1" t="s">
         <v>1695</v>
       </c>
-      <c r="E444" s="1" t="s">
+      <c r="B445" s="1" t="s">
         <v>1696</v>
       </c>
-    </row>
-    <row r="445" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A445" s="1" t="s">
+      <c r="C445" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D445" s="1" t="s">
         <v>1697</v>
       </c>
-      <c r="B445" s="1" t="s">
+      <c r="E445" s="1" t="s">
         <v>1698</v>
       </c>
-      <c r="C445" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D445" s="1" t="s">
+    </row>
+    <row r="446" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A446" s="1" t="s">
         <v>1699</v>
       </c>
-      <c r="E445" s="1" t="s">
+      <c r="B446" s="1" t="s">
         <v>1700</v>
       </c>
-    </row>
-    <row r="446" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A446" s="1" t="s">
+      <c r="C446" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D446" s="1" t="s">
         <v>1701</v>
       </c>
-      <c r="B446" s="1" t="s">
+      <c r="E446" s="1" t="s">
         <v>1702</v>
       </c>
-      <c r="C446" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D446" s="1" t="s">
+    </row>
+    <row r="447" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A447" s="1" t="s">
         <v>1703</v>
       </c>
-      <c r="E446" s="1" t="s">
+      <c r="B447" s="1" t="s">
         <v>1704</v>
       </c>
-    </row>
-    <row r="447" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A447" s="1" t="s">
+      <c r="C447" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D447" s="1" t="s">
         <v>1705</v>
       </c>
-      <c r="B447" s="1" t="s">
+      <c r="E447" s="1" t="s">
         <v>1706</v>
       </c>
-      <c r="C447" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D447" s="1" t="s">
+    </row>
+    <row r="448" spans="1:5" ht="315" x14ac:dyDescent="0.25">
+      <c r="A448" s="1" t="s">
         <v>1707</v>
       </c>
-      <c r="E447" s="1" t="s">
+      <c r="B448" s="1" t="s">
         <v>1708</v>
       </c>
-    </row>
-    <row r="448" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A448" s="1" t="s">
+      <c r="C448" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D448" s="1" t="s">
         <v>1709</v>
       </c>
-      <c r="B448" s="1" t="s">
+      <c r="E448" s="1" t="s">
         <v>1710</v>
       </c>
-      <c r="C448" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D448" s="1" t="s">
+    </row>
+    <row r="449" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A449" s="1" t="s">
         <v>1711</v>
       </c>
-      <c r="E448" s="1" t="s">
+      <c r="B449" s="1" t="s">
         <v>1712</v>
       </c>
-    </row>
-    <row r="449" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A449" s="1" t="s">
+      <c r="C449" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D449" s="1" t="s">
         <v>1713</v>
       </c>
-      <c r="B449" s="1" t="s">
+      <c r="E449" s="1" t="s">
         <v>1714</v>
       </c>
-      <c r="C449" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D449" s="1" t="s">
+    </row>
+    <row r="450" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A450" s="1" t="s">
         <v>1715</v>
       </c>
-      <c r="E449" s="1" t="s">
+      <c r="B450" s="1" t="s">
         <v>1716</v>
       </c>
-    </row>
-    <row r="450" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A450" s="1" t="s">
+      <c r="C450" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D450" s="1" t="s">
         <v>1717</v>
       </c>
-      <c r="B450" s="1" t="s">
+      <c r="E450" s="1" t="s">
         <v>1718</v>
       </c>
-      <c r="C450" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D450" s="1" t="s">
+    </row>
+    <row r="451" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A451" s="1" t="s">
         <v>1719</v>
       </c>
-      <c r="E450" s="1" t="s">
+      <c r="B451" s="1" t="s">
         <v>1720</v>
-      </c>
-    </row>
-    <row r="451" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A451" s="1" t="s">
-        <v>1721</v>
-      </c>
-      <c r="B451" s="1" t="s">
-        <v>1722</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D451" s="1" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E451" s="1" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A452" s="1" t="s">
         <v>1723</v>
       </c>
-      <c r="E451" s="1" t="s">
+      <c r="B452" s="1" t="s">
         <v>1724</v>
-      </c>
-    </row>
-    <row r="452" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A452" s="1" t="s">
-        <v>1725</v>
-      </c>
-      <c r="B452" s="1" t="s">
-        <v>1726</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D452" s="1" t="s">
+        <v>1725</v>
+      </c>
+      <c r="E452" s="1" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A453" s="1" t="s">
         <v>1727</v>
       </c>
-      <c r="E452" s="1" t="s">
+      <c r="B453" s="1" t="s">
         <v>1728</v>
       </c>
-    </row>
-    <row r="453" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A453" s="1" t="s">
+      <c r="C453" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D453" s="1" t="s">
         <v>1729</v>
       </c>
-      <c r="B453" s="1" t="s">
+      <c r="E453" s="1" t="s">
         <v>1730</v>
       </c>
-      <c r="C453" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D453" s="1" t="s">
+    </row>
+    <row r="454" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A454" s="1" t="s">
         <v>1731</v>
       </c>
-      <c r="E453" s="1" t="s">
+      <c r="B454" s="1" t="s">
         <v>1732</v>
       </c>
-    </row>
-    <row r="454" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A454" s="1" t="s">
+      <c r="C454" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D454" s="1" t="s">
         <v>1733</v>
       </c>
-      <c r="B454" s="1" t="s">
+      <c r="E454" s="1" t="s">
         <v>1734</v>
       </c>
-      <c r="C454" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D454" s="1" t="s">
+    </row>
+    <row r="455" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A455" s="1" t="s">
         <v>1735</v>
       </c>
-      <c r="E454" s="1" t="s">
+      <c r="B455" s="1" t="s">
         <v>1736</v>
       </c>
-    </row>
-    <row r="455" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A455" s="1" t="s">
+      <c r="C455" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D455" s="1" t="s">
         <v>1737</v>
       </c>
-      <c r="B455" s="1" t="s">
+      <c r="E455" s="1" t="s">
         <v>1738</v>
       </c>
-      <c r="C455" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D455" s="1" t="s">
+    </row>
+    <row r="456" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A456" s="1" t="s">
         <v>1739</v>
       </c>
-      <c r="E455" s="1" t="s">
+      <c r="B456" s="1" t="s">
         <v>1740</v>
       </c>
-    </row>
-    <row r="456" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A456" s="1" t="s">
+      <c r="C456" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D456" s="1" t="s">
         <v>1741</v>
       </c>
-      <c r="B456" s="1" t="s">
+      <c r="E456" s="1" t="s">
         <v>1742</v>
       </c>
-      <c r="C456" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D456" s="1" t="s">
+    </row>
+    <row r="457" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A457" s="1" t="s">
         <v>1743</v>
       </c>
-      <c r="E456" s="1" t="s">
+      <c r="B457" s="1" t="s">
         <v>1744</v>
-      </c>
-    </row>
-    <row r="457" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A457" s="1" t="s">
-        <v>1745</v>
-      </c>
-      <c r="B457" s="1" t="s">
-        <v>1746</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D457" s="1" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E457" s="1" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A458" s="1" t="s">
         <v>1747</v>
       </c>
-      <c r="E457" s="1" t="s">
+      <c r="B458" s="1" t="s">
         <v>1748</v>
-      </c>
-    </row>
-    <row r="458" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A458" s="1" t="s">
-        <v>1749</v>
-      </c>
-      <c r="B458" s="1" t="s">
-        <v>1750</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D458" s="1" t="s">
+        <v>1749</v>
+      </c>
+      <c r="E458" s="1" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A459" s="1" t="s">
         <v>1751</v>
       </c>
-      <c r="E458" s="1" t="s">
+      <c r="B459" s="1" t="s">
         <v>1752</v>
-      </c>
-    </row>
-    <row r="459" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A459" s="1" t="s">
-        <v>1753</v>
-      </c>
-      <c r="B459" s="1" t="s">
-        <v>1754</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D459" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="E459" s="1" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A460" s="1" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B460" s="1" t="s">
         <v>1755</v>
-      </c>
-      <c r="E459" s="1" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="460" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A460" s="1" t="s">
-        <v>1756</v>
-      </c>
-      <c r="B460" s="1" t="s">
-        <v>1757</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D460" s="1" t="s">
+        <v>1756</v>
+      </c>
+      <c r="E460" s="1" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A461" s="1" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B461" s="1" t="s">
         <v>1758</v>
       </c>
-      <c r="E460" s="1" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="461" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A461" s="1" t="s">
+      <c r="C461" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D461" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="B461" s="1" t="s">
+      <c r="E461" s="1" t="s">
         <v>1760</v>
       </c>
-      <c r="C461" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D461" s="1" t="s">
+    </row>
+    <row r="462" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A462" s="1" t="s">
         <v>1761</v>
       </c>
-      <c r="E461" s="1" t="s">
+      <c r="B462" s="1" t="s">
         <v>1762</v>
-      </c>
-    </row>
-    <row r="462" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A462" s="1" t="s">
-        <v>1763</v>
-      </c>
-      <c r="B462" s="1" t="s">
-        <v>1764</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D462" s="1" t="s">
+        <v>1763</v>
+      </c>
+      <c r="E462" s="1"/>
+    </row>
+    <row r="463" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A463" s="1" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B463" s="1" t="s">
         <v>1765</v>
       </c>
-      <c r="E462" s="1"/>
-    </row>
-    <row r="463" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A463" s="1" t="s">
+      <c r="C463" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D463" s="1" t="s">
         <v>1766</v>
       </c>
-      <c r="B463" s="1" t="s">
+      <c r="E463" s="1" t="s">
         <v>1767</v>
       </c>
-      <c r="C463" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D463" s="1" t="s">
+    </row>
+    <row r="464" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A464" s="1" t="s">
         <v>1768</v>
       </c>
-      <c r="E463" s="1" t="s">
+      <c r="B464" s="1" t="s">
         <v>1769</v>
       </c>
-    </row>
-    <row r="464" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A464" s="1" t="s">
+      <c r="C464" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D464" s="1" t="s">
         <v>1770</v>
       </c>
-      <c r="B464" s="1" t="s">
+      <c r="E464" s="1" t="s">
         <v>1771</v>
       </c>
-      <c r="C464" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D464" s="1" t="s">
+    </row>
+    <row r="465" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A465" s="1" t="s">
         <v>1772</v>
       </c>
-      <c r="E464" s="1" t="s">
+      <c r="B465" s="1" t="s">
         <v>1773</v>
       </c>
-    </row>
-    <row r="465" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A465" s="1" t="s">
+      <c r="C465" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D465" s="1" t="s">
         <v>1774</v>
       </c>
-      <c r="B465" s="1" t="s">
+      <c r="E465" s="1" t="s">
         <v>1775</v>
       </c>
-      <c r="C465" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D465" s="1" t="s">
+    </row>
+    <row r="466" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A466" s="1" t="s">
         <v>1776</v>
       </c>
-      <c r="E465" s="1" t="s">
+      <c r="B466" s="1" t="s">
         <v>1777</v>
       </c>
-    </row>
-    <row r="466" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A466" s="1" t="s">
+      <c r="C466" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D466" s="1" t="s">
         <v>1778</v>
       </c>
-      <c r="B466" s="1" t="s">
+      <c r="E466" s="1" t="s">
         <v>1779</v>
       </c>
-      <c r="C466" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D466" s="1" t="s">
+    </row>
+    <row r="467" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A467" s="1" t="s">
         <v>1780</v>
       </c>
-      <c r="E466" s="1" t="s">
+      <c r="B467" s="1" t="s">
         <v>1781</v>
       </c>
-    </row>
-    <row r="467" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A467" s="1" t="s">
+      <c r="C467" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D467" s="1" t="s">
         <v>1782</v>
       </c>
-      <c r="B467" s="1" t="s">
+      <c r="E467" s="1" t="s">
         <v>1783</v>
       </c>
-      <c r="C467" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D467" s="1" t="s">
+    </row>
+    <row r="468" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A468" s="1" t="s">
         <v>1784</v>
       </c>
-      <c r="E467" s="1" t="s">
+      <c r="B468" s="1" t="s">
         <v>1785</v>
       </c>
-    </row>
-    <row r="468" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A468" s="1" t="s">
+      <c r="C468" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D468" s="1" t="s">
         <v>1786</v>
       </c>
-      <c r="B468" s="1" t="s">
+      <c r="E468" s="1" t="s">
         <v>1787</v>
       </c>
-      <c r="C468" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D468" s="1" t="s">
+    </row>
+    <row r="469" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A469" s="1" t="s">
         <v>1788</v>
       </c>
-      <c r="E468" s="1" t="s">
+      <c r="B469" s="1" t="s">
         <v>1789</v>
       </c>
-    </row>
-    <row r="469" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A469" s="1" t="s">
+      <c r="C469" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D469" s="1" t="s">
         <v>1790</v>
       </c>
-      <c r="B469" s="1" t="s">
+      <c r="E469" s="1" t="s">
         <v>1791</v>
       </c>
-      <c r="C469" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D469" s="1" t="s">
+    </row>
+    <row r="470" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A470" s="1" t="s">
         <v>1792</v>
       </c>
-      <c r="E469" s="1" t="s">
+      <c r="B470" s="1" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="470" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A470" s="1" t="s">
+      <c r="C470" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D470" s="1" t="s">
         <v>1794</v>
       </c>
-      <c r="B470" s="1" t="s">
-        <v>1795</v>
-      </c>
-      <c r="C470" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D470" s="1" t="s">
-        <v>1796</v>
-      </c>
       <c r="E470" s="1" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
     </row>
   </sheetData>

--- a/Audit Checklist in Excel/security_audit_requirements.xlsx
+++ b/Audit Checklist in Excel/security_audit_requirements.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1\repositorios\SECM-CAT\Audit Checklist in Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1\repositorios\paper3_14_07_2026\SECM-CAT\Audit Checklist in Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409489F8-C9BF-4AFE-BF00-9C289E477BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C307E23-A6DD-45B6-8629-487A7E391974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
